--- a/results.xlsx
+++ b/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\GeoGNNGraphDetect\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73406D97-87C4-4211-95B4-40323B264E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7141DD5F-2A70-BF4D-8960-EF775AD7A2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,6 +68,30 @@
   </si>
   <si>
     <t>Geo_reg10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reg=100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>epoch=100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>no_2l_multiN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>all_2l</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Full</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -78,7 +102,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,6 +123,24 @@
       <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="4"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -123,13 +165,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -410,31 +454,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.64453125" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="8.9375" style="1"/>
+    <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="3"/>
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="G1" s="3"/>
+      <c r="I1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -456,8 +503,11 @@
       <c r="G2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -479,8 +529,11 @@
       <c r="G3" s="1">
         <v>4.3799999999999999E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="I3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -503,7 +556,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -513,27 +566,27 @@
       <c r="C5" s="1">
         <v>6.3700000000000007E-2</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>0.73909999999999998</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>5.6399999999999999E-2</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>0.70789999999999997</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>4.5900000000000003E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>0.74790000000000001</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>6.5199999999999994E-2</v>
       </c>
       <c r="D6" s="1">
@@ -547,6 +600,75 @@
       </c>
       <c r="G6" s="1">
         <v>3.8100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1">
+        <v>0.72529999999999994</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.71630000000000005</v>
+      </c>
+      <c r="E7" s="1">
+        <v>4.7E-2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.71379999999999999</v>
+      </c>
+      <c r="G7" s="1">
+        <v>3.6600000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1">
+        <v>0.72940000000000005</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5.4300000000000001E-2</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.72109999999999996</v>
+      </c>
+      <c r="E8" s="1">
+        <v>5.0900000000000001E-2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.65710000000000002</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4">
+        <v>0.74460000000000004</v>
+      </c>
+      <c r="C9" s="4">
+        <v>6.3700000000000007E-2</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.73919999999999997</v>
+      </c>
+      <c r="E9" s="4">
+        <v>5.62E-2</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.71989999999999998</v>
+      </c>
+      <c r="G9" s="4">
+        <v>4.6300000000000001E-2</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -169,11 +169,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -465,18 +465,18 @@
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3"/>
+      <c r="G1" s="5"/>
       <c r="I1" s="1" t="s">
         <v>11</v>
       </c>
@@ -618,7 +618,7 @@
       <c r="E7" s="1">
         <v>4.7E-2</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>0.71379999999999999</v>
       </c>
       <c r="G7" s="1">
@@ -652,22 +652,22 @@
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>0.74460000000000004</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>6.3700000000000007E-2</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>0.73919999999999997</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>5.62E-2</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <v>0.71989999999999998</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="3">
         <v>4.6300000000000001E-2</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7141DD5F-2A70-BF4D-8960-EF775AD7A2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F840BA0-E2BB-F042-A0E8-03634FDFFDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10300" yWindow="1200" windowWidth="21420" windowHeight="16780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,16 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>data</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>graph1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -51,10 +47,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rec1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Geo_reg1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -92,6 +84,45 @@
   </si>
   <si>
     <t>Full</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>top2% Classicification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rec2%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PRAUC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pre2%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F1-2%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>MMOE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+      </rPr>
+      <t>架构</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Data</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -118,42 +149,52 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -161,19 +202,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -454,228 +520,239 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:R10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="1"/>
+    <col min="2" max="6" width="9" style="6"/>
+    <col min="7" max="11" width="9" style="7"/>
+    <col min="12" max="16" width="9" style="8"/>
+    <col min="17" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5" t="s">
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5"/>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="R1" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="R4" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="R5" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0.74629999999999996</v>
-      </c>
-      <c r="C3" s="1">
-        <v>6.3399999999999998E-2</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.73880000000000001</v>
-      </c>
-      <c r="E3" s="1">
-        <v>5.6399999999999999E-2</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0.70650000000000002</v>
-      </c>
-      <c r="G3" s="1">
-        <v>4.3799999999999999E-2</v>
-      </c>
-      <c r="I3" s="1" t="s">
+    <row r="8" spans="1:18">
+      <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0.74639999999999995</v>
-      </c>
-      <c r="C4" s="1">
-        <v>6.4100000000000004E-2</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.7389</v>
-      </c>
-      <c r="E4" s="1">
-        <v>5.6000000000000001E-2</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.70640000000000003</v>
-      </c>
-      <c r="G4" s="1">
-        <v>3.7499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.74619999999999997</v>
-      </c>
-      <c r="C5" s="1">
-        <v>6.3700000000000007E-2</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.73909999999999998</v>
-      </c>
-      <c r="E5" s="2">
-        <v>5.6399999999999999E-2</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0.70789999999999997</v>
-      </c>
-      <c r="G5" s="2">
-        <v>4.5900000000000003E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0.74790000000000001</v>
-      </c>
-      <c r="C6" s="2">
-        <v>6.5199999999999994E-2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.73699999999999999</v>
-      </c>
-      <c r="E6" s="1">
-        <v>5.62E-2</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0.70079999999999998</v>
-      </c>
-      <c r="G6" s="1">
-        <v>3.8100000000000002E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
+    <row r="9" spans="1:18">
+      <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="1">
-        <v>0.72529999999999994</v>
-      </c>
-      <c r="C7" s="1">
-        <v>5.3900000000000003E-2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0.71630000000000005</v>
-      </c>
-      <c r="E7" s="1">
-        <v>4.7E-2</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0.71379999999999999</v>
-      </c>
-      <c r="G7" s="1">
-        <v>3.6600000000000001E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0.72940000000000005</v>
-      </c>
-      <c r="C8" s="1">
-        <v>5.4300000000000001E-2</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0.72109999999999996</v>
-      </c>
-      <c r="E8" s="1">
-        <v>5.0900000000000001E-2</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0.65710000000000002</v>
-      </c>
-      <c r="G8" s="1">
-        <v>2.7E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0.74460000000000004</v>
-      </c>
-      <c r="C9" s="3">
-        <v>6.3700000000000007E-2</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0.73919999999999997</v>
-      </c>
-      <c r="E9" s="3">
-        <v>5.62E-2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.71989999999999998</v>
-      </c>
-      <c r="G9" s="3">
-        <v>4.6300000000000001E-2</v>
+      <c r="B9" s="9">
+        <v>0.74039999999999995</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.1033</v>
+      </c>
+      <c r="D9" s="9">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="E9" s="9">
+        <v>3.39E-2</v>
+      </c>
+      <c r="F9" s="9">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0.73829999999999996</v>
+      </c>
+      <c r="H9" s="10">
+        <v>8.3699999999999997E-2</v>
+      </c>
+      <c r="I9" s="10">
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="J9" s="10">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="K9" s="10">
+        <v>4.7899999999999998E-2</v>
+      </c>
+      <c r="L9" s="11">
+        <v>0.70309999999999995</v>
+      </c>
+      <c r="M9" s="11">
+        <v>6.3600000000000004E-2</v>
+      </c>
+      <c r="N9" s="11">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="O9" s="11">
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="P9" s="11">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0.68120000000000003</v>
+      </c>
+      <c r="C10" s="6">
+        <v>7.4899999999999994E-2</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1.6E-2</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.47E-2</v>
+      </c>
+      <c r="F10" s="6">
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0.69889999999999997</v>
+      </c>
+      <c r="H10" s="7">
+        <v>7.1499999999999994E-2</v>
+      </c>
+      <c r="I10" s="7">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="J10" s="7">
+        <v>2.86E-2</v>
+      </c>
+      <c r="K10" s="7">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="L10" s="8">
+        <v>0.62560000000000004</v>
+      </c>
+      <c r="M10" s="8">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="N10" s="8">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O10" s="8">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="P10" s="8">
+        <v>3.5900000000000001E-2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="L1:P1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F840BA0-E2BB-F042-A0E8-03634FDFFDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10300" yWindow="1200" windowWidth="21420" windowHeight="16780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -224,6 +224,13 @@
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -233,13 +240,6 @@
     <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -524,38 +524,38 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
-    <col min="2" max="6" width="9" style="6"/>
-    <col min="7" max="11" width="9" style="7"/>
-    <col min="12" max="16" width="9" style="8"/>
-    <col min="17" max="16384" width="9" style="5"/>
+    <col min="2" max="6" width="9" style="3"/>
+    <col min="7" max="11" width="9" style="4"/>
+    <col min="12" max="16" width="9" style="5"/>
+    <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3" t="s">
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="4" t="s">
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="R1" s="5" t="s">
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="R1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -563,52 +563,52 @@
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -621,7 +621,7 @@
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="R4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -629,7 +629,7 @@
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="R5" s="2" t="s">
         <v>11</v>
       </c>
     </row>
@@ -652,49 +652,49 @@
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="6">
         <v>0.74039999999999995</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="6">
         <v>0.1033</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="6">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="6">
         <v>3.39E-2</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="6">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="7">
         <v>0.73829999999999996</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="7">
         <v>8.3699999999999997E-2</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="7">
         <v>2.2599999999999999E-2</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="7">
         <v>3.3599999999999998E-2</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="7">
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="L9" s="11">
+      <c r="L9" s="8">
         <v>0.70309999999999995</v>
       </c>
-      <c r="M9" s="11">
+      <c r="M9" s="8">
         <v>6.3600000000000004E-2</v>
       </c>
-      <c r="N9" s="11">
+      <c r="N9" s="8">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="O9" s="11">
+      <c r="O9" s="8">
         <v>5.3400000000000003E-2</v>
       </c>
-      <c r="P9" s="11">
+      <c r="P9" s="8">
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
@@ -702,49 +702,49 @@
       <c r="A10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="3">
         <v>0.68120000000000003</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="3">
         <v>7.4899999999999994E-2</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="3">
         <v>1.6E-2</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="3">
         <v>2.47E-2</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="3">
         <v>3.7100000000000001E-2</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="4">
         <v>0.69889999999999997</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="4">
         <v>7.1499999999999994E-2</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="4">
         <v>1.9800000000000002E-2</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="4">
         <v>2.86E-2</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="4">
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="5">
         <v>0.62560000000000004</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="5">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N10" s="5">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="5">
         <v>3.3099999999999997E-2</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P10" s="5">
         <v>3.5900000000000001E-2</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F840BA0-E2BB-F042-A0E8-03634FDFFDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379C01CA-1A1D-BA40-A389-E26BBCBC003C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-740" yWindow="660" windowWidth="19300" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -79,10 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>all_2l</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Full</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -123,6 +119,10 @@
   </si>
   <si>
     <t>Data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FullnoReg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -532,7 +532,7 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1</v>
@@ -567,49 +567,49 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="R2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -645,44 +645,89 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="B8" s="6">
+        <v>0.74299999999999999</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.1057</v>
+      </c>
+      <c r="D8" s="6">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="E8" s="6">
+        <v>3.4700000000000002E-2</v>
+      </c>
+      <c r="F8" s="6">
+        <v>5.2299999999999999E-2</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0.73850000000000005</v>
+      </c>
+      <c r="H8" s="7">
+        <v>8.9599999999999999E-2</v>
+      </c>
+      <c r="I8" s="7">
+        <v>2.3E-2</v>
+      </c>
+      <c r="J8" s="7">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="K8" s="7">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="L8" s="8">
+        <v>0.70840000000000003</v>
+      </c>
+      <c r="M8" s="5">
+        <v>6.1800000000000001E-2</v>
+      </c>
+      <c r="N8" s="5">
+        <v>3.8199999999999998E-2</v>
+      </c>
+      <c r="O8" s="5">
+        <v>5.1700000000000003E-2</v>
+      </c>
+      <c r="P8" s="5">
+        <v>5.6300000000000003E-2</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="6">
+        <v>13</v>
+      </c>
+      <c r="B9" s="3">
         <v>0.74039999999999995</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="3">
         <v>0.1033</v>
       </c>
       <c r="D9" s="6">
         <v>2.0299999999999999E-2</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="3">
         <v>3.39E-2</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="3">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="4">
         <v>0.73829999999999996</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="4">
         <v>8.3699999999999997E-2</v>
       </c>
-      <c r="I9" s="7">
+      <c r="I9" s="4">
         <v>2.2599999999999999E-2</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="4">
         <v>3.3599999999999998E-2</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="4">
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="5">
         <v>0.70309999999999995</v>
       </c>
       <c r="M9" s="8">
@@ -700,7 +745,7 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="3">
         <v>0.68120000000000003</v>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379C01CA-1A1D-BA40-A389-E26BBCBC003C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96449EF-770F-E94E-A33F-2005A2B7ACA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-740" yWindow="660" windowWidth="19300" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="19300" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -122,7 +122,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FullnoReg</t>
+    <t>Full-oth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Full-oth-wei</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -520,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
@@ -645,151 +649,201 @@
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="6">
-        <v>0.74299999999999999</v>
+        <v>0.74919999999999998</v>
       </c>
       <c r="C8" s="6">
-        <v>0.1057</v>
+        <v>0.1119</v>
       </c>
       <c r="D8" s="6">
-        <v>2.0299999999999999E-2</v>
+        <v>2.06E-2</v>
       </c>
       <c r="E8" s="6">
-        <v>3.4700000000000002E-2</v>
+        <v>3.6799999999999999E-2</v>
       </c>
       <c r="F8" s="6">
-        <v>5.2299999999999999E-2</v>
+        <v>5.5399999999999998E-2</v>
       </c>
       <c r="G8" s="7">
-        <v>0.73850000000000005</v>
+        <v>0.74590000000000001</v>
       </c>
       <c r="H8" s="7">
-        <v>8.9599999999999999E-2</v>
-      </c>
-      <c r="I8" s="7">
-        <v>2.3E-2</v>
+        <v>9.0200000000000002E-2</v>
+      </c>
+      <c r="I8" s="4">
+        <v>2.3300000000000001E-2</v>
       </c>
       <c r="J8" s="7">
-        <v>3.5900000000000001E-2</v>
+        <v>3.6200000000000003E-2</v>
       </c>
       <c r="K8" s="7">
-        <v>5.1299999999999998E-2</v>
+        <v>5.16E-2</v>
       </c>
       <c r="L8" s="8">
-        <v>0.70840000000000003</v>
+        <v>0.71619999999999995</v>
       </c>
       <c r="M8" s="5">
-        <v>6.1800000000000001E-2</v>
-      </c>
-      <c r="N8" s="5">
-        <v>3.8199999999999998E-2</v>
+        <v>6.6799999999999998E-2</v>
+      </c>
+      <c r="N8" s="8">
+        <v>3.9100000000000003E-2</v>
       </c>
       <c r="O8" s="5">
-        <v>5.1700000000000003E-2</v>
+        <v>5.57E-2</v>
       </c>
       <c r="P8" s="5">
-        <v>5.6300000000000003E-2</v>
+        <v>6.0699999999999997E-2</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B9" s="3">
-        <v>0.74039999999999995</v>
+        <v>0.74709999999999999</v>
       </c>
       <c r="C9" s="3">
-        <v>0.1033</v>
+        <v>0.10970000000000001</v>
       </c>
       <c r="D9" s="6">
-        <v>2.0299999999999999E-2</v>
+        <v>2.06E-2</v>
       </c>
       <c r="E9" s="3">
-        <v>3.39E-2</v>
+        <v>3.61E-2</v>
       </c>
       <c r="F9" s="3">
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.73829999999999996</v>
+        <v>5.4300000000000001E-2</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0.74590000000000001</v>
       </c>
       <c r="H9" s="4">
-        <v>8.3699999999999997E-2</v>
-      </c>
-      <c r="I9" s="4">
-        <v>2.2599999999999999E-2</v>
+        <v>9.01E-2</v>
+      </c>
+      <c r="I9" s="7">
+        <v>2.3400000000000001E-2</v>
       </c>
       <c r="J9" s="4">
-        <v>3.3599999999999998E-2</v>
-      </c>
-      <c r="K9" s="4">
-        <v>4.7899999999999998E-2</v>
+        <v>3.61E-2</v>
+      </c>
+      <c r="K9" s="7">
+        <v>5.1499999999999997E-2</v>
       </c>
       <c r="L9" s="5">
-        <v>0.70309999999999995</v>
+        <v>0.71040000000000003</v>
       </c>
       <c r="M9" s="8">
-        <v>6.3600000000000004E-2</v>
-      </c>
-      <c r="N9" s="8">
-        <v>3.9399999999999998E-2</v>
+        <v>6.7100000000000007E-2</v>
+      </c>
+      <c r="N9" s="5">
+        <v>3.8100000000000002E-2</v>
       </c>
       <c r="O9" s="8">
-        <v>5.3400000000000003E-2</v>
+        <v>5.6300000000000003E-2</v>
       </c>
       <c r="P9" s="8">
-        <v>5.8000000000000003E-2</v>
+        <v>6.1199999999999997E-2</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.74039999999999995</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.1033</v>
+      </c>
+      <c r="D10" s="6">
+        <v>2.0299999999999999E-2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.39E-2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.73829999999999996</v>
+      </c>
+      <c r="H10" s="4">
+        <v>8.3699999999999997E-2</v>
+      </c>
+      <c r="I10" s="4">
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="J10" s="4">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="K10" s="4">
+        <v>4.7899999999999998E-2</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0.70309999999999995</v>
+      </c>
+      <c r="M10" s="5">
+        <v>6.3600000000000004E-2</v>
+      </c>
+      <c r="N10" s="8">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="O10" s="5">
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="P10" s="5">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B11" s="3">
         <v>0.68120000000000003</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C11" s="3">
         <v>7.4899999999999994E-2</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D11" s="3">
         <v>1.6E-2</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E11" s="3">
         <v>2.47E-2</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F11" s="3">
         <v>3.7100000000000001E-2</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G11" s="4">
         <v>0.69889999999999997</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H11" s="4">
         <v>7.1499999999999994E-2</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I11" s="4">
         <v>1.9800000000000002E-2</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J11" s="4">
         <v>2.86E-2</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K11" s="4">
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L11" s="5">
         <v>0.62560000000000004</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M11" s="5">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N11" s="5">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O11" s="5">
         <v>3.3099999999999997E-2</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P11" s="5">
         <v>3.5900000000000001E-2</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96449EF-770F-E94E-A33F-2005A2B7ACA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="19300" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96449EF-770F-E94E-A33F-2005A2B7ACA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2584382-AA8C-274F-81E3-CAB05F44429E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5240" yWindow="-16360" windowWidth="51200" windowHeight="26580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -47,35 +47,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Geo_reg1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Geo_reg100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Geo_reg0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Geo_reg10000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>reg=100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>epoch=100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>no_2l_multiN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -127,6 +99,30 @@
   </si>
   <si>
     <t>Full-oth-wei</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Full_ClaOth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Full_noOth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reg=0.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Full_ClaOth_Reg=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Full_ClaOth_Reg=1e-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>epoch=200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -524,10 +520,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
     <col min="2" max="6" width="9" style="3"/>
     <col min="7" max="11" width="9" style="4"/>
     <col min="12" max="16" width="9" style="5"/>
@@ -536,7 +532,7 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>1</v>
@@ -560,7 +556,7 @@
       <c r="O1" s="11"/>
       <c r="P1" s="11"/>
       <c r="R1" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -571,279 +567,454 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.75229999999999997</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.1023</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2.06E-2</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>5.0599999999999999E-2</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.749</v>
+      </c>
+      <c r="H3" s="4">
+        <v>8.9599999999999999E-2</v>
+      </c>
+      <c r="I3" s="4">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="J3" s="4">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="K3" s="4">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0.72460000000000002</v>
+      </c>
+      <c r="M3" s="8">
+        <v>7.22E-2</v>
+      </c>
+      <c r="N3" s="8">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="O3" s="8">
+        <v>6.0400000000000002E-2</v>
+      </c>
+      <c r="P3" s="8">
+        <v>6.5699999999999995E-2</v>
       </c>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.75170000000000003</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.1055</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2.06E-2</v>
+      </c>
+      <c r="E4" s="3">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>5.21E-2</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.749</v>
+      </c>
+      <c r="H4" s="4">
+        <v>8.9399999999999993E-2</v>
+      </c>
+      <c r="I4" s="4">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="J4" s="4">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="K4" s="4">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0.72509999999999997</v>
+      </c>
+      <c r="M4" s="5">
+        <v>7.1199999999999999E-2</v>
+      </c>
+      <c r="N4" s="5">
+        <v>4.07E-2</v>
+      </c>
+      <c r="O4" s="5">
+        <v>5.9799999999999999E-2</v>
+      </c>
+      <c r="P4" s="5">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.75249999999999995</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.1069</v>
+      </c>
+      <c r="D5" s="3">
+        <v>2.07E-2</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>5.28E-2</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.74860000000000004</v>
+      </c>
+      <c r="H5" s="4">
+        <v>8.9700000000000002E-2</v>
+      </c>
+      <c r="I5" s="7">
+        <v>2.3900000000000001E-2</v>
+      </c>
+      <c r="J5" s="4">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="K5" s="4">
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="L5" s="8">
+        <v>0.72509999999999997</v>
+      </c>
+      <c r="M5" s="5">
+        <v>6.7299999999999999E-2</v>
+      </c>
+      <c r="N5" s="5">
+        <v>4.0599999999999997E-2</v>
+      </c>
+      <c r="O5" s="5">
+        <v>5.62E-2</v>
+      </c>
+      <c r="P5" s="5">
+        <v>6.1199999999999997E-2</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
+      </c>
+      <c r="B6" s="6">
+        <v>0.754</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.10340000000000001</v>
+      </c>
+      <c r="D6" s="6">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="H6" s="4">
+        <v>8.9099999999999999E-2</v>
+      </c>
+      <c r="I6" s="4">
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="J6" s="4">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="K6" s="4">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0.72050000000000003</v>
+      </c>
+      <c r="M6" s="5">
+        <v>6.3399999999999998E-2</v>
+      </c>
+      <c r="N6" s="5">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="O6" s="5">
+        <v>5.2900000000000003E-2</v>
+      </c>
+      <c r="P6" s="5">
+        <v>5.7599999999999998E-2</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.74919999999999998</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.1119</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2.06E-2</v>
+      </c>
+      <c r="E7" s="6">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="F7" s="6">
+        <v>5.5399999999999998E-2</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0.74590000000000001</v>
+      </c>
+      <c r="H7" s="7">
+        <v>9.0200000000000002E-2</v>
+      </c>
+      <c r="I7" s="4">
+        <v>2.3300000000000001E-2</v>
+      </c>
+      <c r="J7" s="7">
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="K7" s="7">
+        <v>5.16E-2</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0.71619999999999995</v>
+      </c>
+      <c r="M7" s="5">
+        <v>6.6799999999999998E-2</v>
+      </c>
+      <c r="N7" s="5">
+        <v>3.9100000000000003E-2</v>
+      </c>
+      <c r="O7" s="5">
+        <v>5.57E-2</v>
+      </c>
+      <c r="P7" s="5">
+        <v>6.0699999999999997E-2</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0.74919999999999998</v>
-      </c>
-      <c r="C8" s="6">
-        <v>0.1119</v>
-      </c>
-      <c r="D8" s="6">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.74709999999999999</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.10970000000000001</v>
+      </c>
+      <c r="D8" s="3">
         <v>2.06E-2</v>
       </c>
-      <c r="E8" s="6">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="F8" s="6">
-        <v>5.5399999999999998E-2</v>
-      </c>
-      <c r="G8" s="7">
+      <c r="E8" s="3">
+        <v>3.61E-2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5.4300000000000001E-2</v>
+      </c>
+      <c r="G8" s="4">
         <v>0.74590000000000001</v>
       </c>
-      <c r="H8" s="7">
-        <v>9.0200000000000002E-2</v>
+      <c r="H8" s="4">
+        <v>9.01E-2</v>
       </c>
       <c r="I8" s="4">
-        <v>2.3300000000000001E-2</v>
-      </c>
-      <c r="J8" s="7">
-        <v>3.6200000000000003E-2</v>
-      </c>
-      <c r="K8" s="7">
-        <v>5.16E-2</v>
-      </c>
-      <c r="L8" s="8">
-        <v>0.71619999999999995</v>
+        <v>2.3400000000000001E-2</v>
+      </c>
+      <c r="J8" s="4">
+        <v>3.61E-2</v>
+      </c>
+      <c r="K8" s="4">
+        <v>5.1499999999999997E-2</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0.71040000000000003</v>
       </c>
       <c r="M8" s="5">
-        <v>6.6799999999999998E-2</v>
-      </c>
-      <c r="N8" s="8">
-        <v>3.9100000000000003E-2</v>
+        <v>6.7100000000000007E-2</v>
+      </c>
+      <c r="N8" s="5">
+        <v>3.8100000000000002E-2</v>
       </c>
       <c r="O8" s="5">
-        <v>5.57E-2</v>
+        <v>5.6300000000000003E-2</v>
       </c>
       <c r="P8" s="5">
-        <v>6.0699999999999997E-2</v>
+        <v>6.1199999999999997E-2</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B9" s="3">
-        <v>0.74709999999999999</v>
+        <v>0.74039999999999995</v>
       </c>
       <c r="C9" s="3">
-        <v>0.10970000000000001</v>
-      </c>
-      <c r="D9" s="6">
-        <v>2.06E-2</v>
+        <v>0.1033</v>
+      </c>
+      <c r="D9" s="3">
+        <v>2.0299999999999999E-2</v>
       </c>
       <c r="E9" s="3">
-        <v>3.61E-2</v>
+        <v>3.39E-2</v>
       </c>
       <c r="F9" s="3">
-        <v>5.4300000000000001E-2</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0.74590000000000001</v>
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.73829999999999996</v>
       </c>
       <c r="H9" s="4">
-        <v>9.01E-2</v>
-      </c>
-      <c r="I9" s="7">
-        <v>2.3400000000000001E-2</v>
+        <v>8.3699999999999997E-2</v>
+      </c>
+      <c r="I9" s="4">
+        <v>2.2599999999999999E-2</v>
       </c>
       <c r="J9" s="4">
-        <v>3.61E-2</v>
-      </c>
-      <c r="K9" s="7">
-        <v>5.1499999999999997E-2</v>
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="K9" s="4">
+        <v>4.7899999999999998E-2</v>
       </c>
       <c r="L9" s="5">
-        <v>0.71040000000000003</v>
-      </c>
-      <c r="M9" s="8">
-        <v>6.7100000000000007E-2</v>
+        <v>0.70309999999999995</v>
+      </c>
+      <c r="M9" s="5">
+        <v>6.3600000000000004E-2</v>
       </c>
       <c r="N9" s="5">
-        <v>3.8100000000000002E-2</v>
-      </c>
-      <c r="O9" s="8">
-        <v>5.6300000000000003E-2</v>
-      </c>
-      <c r="P9" s="8">
-        <v>6.1199999999999997E-2</v>
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="O9" s="5">
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="P9" s="5">
+        <v>5.8000000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3">
-        <v>0.74039999999999995</v>
+        <v>0.68120000000000003</v>
       </c>
       <c r="C10" s="3">
-        <v>0.1033</v>
-      </c>
-      <c r="D10" s="6">
-        <v>2.0299999999999999E-2</v>
+        <v>7.4899999999999994E-2</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1.6E-2</v>
       </c>
       <c r="E10" s="3">
-        <v>3.39E-2</v>
+        <v>2.47E-2</v>
       </c>
       <c r="F10" s="3">
-        <v>5.0999999999999997E-2</v>
+        <v>3.7100000000000001E-2</v>
       </c>
       <c r="G10" s="4">
-        <v>0.73829999999999996</v>
+        <v>0.69889999999999997</v>
       </c>
       <c r="H10" s="4">
-        <v>8.3699999999999997E-2</v>
+        <v>7.1499999999999994E-2</v>
       </c>
       <c r="I10" s="4">
-        <v>2.2599999999999999E-2</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="J10" s="4">
-        <v>3.3599999999999998E-2</v>
+        <v>2.86E-2</v>
       </c>
       <c r="K10" s="4">
-        <v>4.7899999999999998E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="L10" s="5">
-        <v>0.70309999999999995</v>
+        <v>0.62560000000000004</v>
       </c>
       <c r="M10" s="5">
-        <v>6.3600000000000004E-2</v>
-      </c>
-      <c r="N10" s="8">
         <v>3.9399999999999998E-2</v>
       </c>
+      <c r="N10" s="5">
+        <v>2.9000000000000001E-2</v>
+      </c>
       <c r="O10" s="5">
-        <v>5.3400000000000003E-2</v>
+        <v>3.3099999999999997E-2</v>
       </c>
       <c r="P10" s="5">
-        <v>5.8000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0.68120000000000003</v>
-      </c>
-      <c r="C11" s="3">
-        <v>7.4899999999999994E-2</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1.6E-2</v>
-      </c>
-      <c r="E11" s="3">
-        <v>2.47E-2</v>
-      </c>
-      <c r="F11" s="3">
-        <v>3.7100000000000001E-2</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0.69889999999999997</v>
-      </c>
-      <c r="H11" s="4">
-        <v>7.1499999999999994E-2</v>
-      </c>
-      <c r="I11" s="4">
-        <v>1.9800000000000002E-2</v>
-      </c>
-      <c r="J11" s="4">
-        <v>2.86E-2</v>
-      </c>
-      <c r="K11" s="4">
-        <v>4.0800000000000003E-2</v>
-      </c>
-      <c r="L11" s="5">
-        <v>0.62560000000000004</v>
-      </c>
-      <c r="M11" s="5">
-        <v>3.9399999999999998E-2</v>
-      </c>
-      <c r="N11" s="5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="O11" s="5">
-        <v>3.3099999999999997E-2</v>
-      </c>
-      <c r="P11" s="5">
         <v>3.5900000000000001E-2</v>
       </c>
     </row>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2584382-AA8C-274F-81E3-CAB05F44429E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1171AF6F-87FE-014F-B8DE-197357667F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5240" yWindow="-16360" windowWidth="51200" windowHeight="26580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,33 +26,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>graph1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>graph2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>graph3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>auc</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Full</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -94,14 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Full-oth</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Full-oth-wei</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Full_ClaOth</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -123,6 +100,42 @@
   </si>
   <si>
     <t>epoch=200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>no focr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>no nei</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>no mr1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>no mr2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soc1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Soc2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Com1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朋友友谊关系；商家链接关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sample_weight</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -133,7 +146,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -166,6 +179,13 @@
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="SimSun"/>
+      <family val="1"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
@@ -221,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -240,6 +260,7 @@
     <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -520,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -532,31 +553,31 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
       <c r="F1" s="9"/>
       <c r="G1" s="10" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
       <c r="J1" s="10"/>
       <c r="K1" s="10"/>
       <c r="L1" s="11" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="M1" s="11"/>
       <c r="N1" s="11"/>
       <c r="O1" s="11"/>
       <c r="P1" s="11"/>
       <c r="R1" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -564,57 +585,57 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="I2" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>8</v>
-      </c>
       <c r="N2" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3">
         <v>0.75229999999999997</v>
@@ -652,7 +673,7 @@
       <c r="M3" s="8">
         <v>7.22E-2</v>
       </c>
-      <c r="N3" s="8">
+      <c r="N3" s="5">
         <v>4.1200000000000001E-2</v>
       </c>
       <c r="O3" s="8">
@@ -664,7 +685,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B4" s="3">
         <v>0.75170000000000003</v>
@@ -696,7 +717,7 @@
       <c r="K4" s="4">
         <v>5.1200000000000002E-2</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="5">
         <v>0.72509999999999997</v>
       </c>
       <c r="M4" s="5">
@@ -712,12 +733,12 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3">
         <v>0.75249999999999995</v>
@@ -740,7 +761,7 @@
       <c r="H5" s="4">
         <v>8.9700000000000002E-2</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="4">
         <v>2.3900000000000001E-2</v>
       </c>
       <c r="J5" s="4">
@@ -749,7 +770,7 @@
       <c r="K5" s="4">
         <v>5.1400000000000001E-2</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="5">
         <v>0.72509999999999997</v>
       </c>
       <c r="M5" s="5">
@@ -765,12 +786,12 @@
         <v>6.1199999999999997E-2</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" ht="18" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B6" s="6">
         <v>0.754</v>
@@ -820,122 +841,125 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3">
-        <v>0.74919999999999998</v>
+        <v>0.75070000000000003</v>
       </c>
       <c r="C7" s="6">
-        <v>0.1119</v>
+        <v>0.11070000000000001</v>
       </c>
       <c r="D7" s="3">
         <v>2.06E-2</v>
       </c>
       <c r="E7" s="6">
-        <v>3.6799999999999999E-2</v>
+        <v>3.6499999999999998E-2</v>
       </c>
       <c r="F7" s="6">
-        <v>5.5399999999999998E-2</v>
+        <v>5.4800000000000001E-2</v>
       </c>
       <c r="G7" s="4">
-        <v>0.74590000000000001</v>
-      </c>
-      <c r="H7" s="7">
-        <v>9.0200000000000002E-2</v>
-      </c>
-      <c r="I7" s="4">
-        <v>2.3300000000000001E-2</v>
-      </c>
-      <c r="J7" s="7">
-        <v>3.6200000000000003E-2</v>
-      </c>
-      <c r="K7" s="7">
-        <v>5.16E-2</v>
+        <v>0.74750000000000005</v>
+      </c>
+      <c r="H7" s="4">
+        <v>8.9399999999999993E-2</v>
+      </c>
+      <c r="I7" s="7">
+        <v>2.41E-2</v>
+      </c>
+      <c r="J7" s="4">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="K7" s="4">
+        <v>5.1299999999999998E-2</v>
       </c>
       <c r="L7" s="5">
-        <v>0.71619999999999995</v>
+        <v>0.72130000000000005</v>
       </c>
       <c r="M7" s="5">
-        <v>6.6799999999999998E-2</v>
+        <v>7.1499999999999994E-2</v>
       </c>
       <c r="N7" s="5">
-        <v>3.9100000000000003E-2</v>
-      </c>
-      <c r="O7" s="5">
-        <v>5.57E-2</v>
+        <v>4.0599999999999997E-2</v>
+      </c>
+      <c r="O7" s="8">
+        <v>6.0400000000000002E-2</v>
       </c>
       <c r="P7" s="5">
-        <v>6.0699999999999997E-2</v>
+        <v>6.54E-2</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B8" s="3">
+        <v>0.74770000000000003</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.10340000000000001</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="G8" s="4">
         <v>0.74709999999999999</v>
       </c>
-      <c r="C8" s="3">
-        <v>0.10970000000000001</v>
-      </c>
-      <c r="D8" s="3">
-        <v>2.06E-2</v>
-      </c>
-      <c r="E8" s="3">
-        <v>3.61E-2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>5.4300000000000001E-2</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0.74590000000000001</v>
-      </c>
-      <c r="H8" s="4">
-        <v>9.01E-2</v>
+      <c r="H8" s="7">
+        <v>9.1499999999999998E-2</v>
       </c>
       <c r="I8" s="4">
-        <v>2.3400000000000001E-2</v>
-      </c>
-      <c r="J8" s="4">
-        <v>3.61E-2</v>
-      </c>
-      <c r="K8" s="4">
-        <v>5.1499999999999997E-2</v>
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="J8" s="7">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="K8" s="7">
+        <v>5.2400000000000002E-2</v>
       </c>
       <c r="L8" s="5">
-        <v>0.71040000000000003</v>
+        <v>0.71550000000000002</v>
       </c>
       <c r="M8" s="5">
-        <v>6.7100000000000007E-2</v>
+        <v>6.9099999999999995E-2</v>
       </c>
       <c r="N8" s="5">
-        <v>3.8100000000000002E-2</v>
+        <v>4.0500000000000001E-2</v>
       </c>
       <c r="O8" s="5">
-        <v>5.6300000000000003E-2</v>
+        <v>5.8099999999999999E-2</v>
       </c>
       <c r="P8" s="5">
-        <v>6.1199999999999997E-2</v>
+        <v>6.3100000000000003E-2</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B9" s="3">
-        <v>0.74039999999999995</v>
+        <v>0.74580000000000002</v>
       </c>
       <c r="C9" s="3">
-        <v>0.1033</v>
+        <v>9.6299999999999997E-2</v>
       </c>
       <c r="D9" s="3">
-        <v>2.0299999999999999E-2</v>
+        <v>1.9900000000000001E-2</v>
       </c>
       <c r="E9" s="3">
-        <v>3.39E-2</v>
+        <v>3.1800000000000002E-2</v>
       </c>
       <c r="F9" s="3">
-        <v>5.0999999999999997E-2</v>
+        <v>4.7800000000000002E-2</v>
       </c>
       <c r="G9" s="4">
         <v>0.73829999999999996</v>
@@ -953,69 +977,169 @@
         <v>4.7899999999999998E-2</v>
       </c>
       <c r="L9" s="5">
-        <v>0.70309999999999995</v>
+        <v>0.71079999999999999</v>
       </c>
       <c r="M9" s="5">
-        <v>6.3600000000000004E-2</v>
+        <v>5.96E-2</v>
       </c>
       <c r="N9" s="5">
-        <v>3.9399999999999998E-2</v>
+        <v>3.6799999999999999E-2</v>
       </c>
       <c r="O9" s="5">
-        <v>5.3400000000000003E-2</v>
+        <v>4.8599999999999997E-2</v>
       </c>
       <c r="P9" s="5">
-        <v>5.8000000000000003E-2</v>
+        <v>5.3499999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B10" s="3">
+        <v>7.4709999999999999E-2</v>
+      </c>
+      <c r="C10" s="3">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.1699999999999999E-2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>4.7600000000000003E-2</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.74260000000000004</v>
+      </c>
+      <c r="H10" s="4">
+        <v>7.9899999999999999E-2</v>
+      </c>
+      <c r="I10" s="4">
+        <v>2.2100000000000002E-2</v>
+      </c>
+      <c r="J10" s="4">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="K10" s="4">
+        <v>4.58E-2</v>
+      </c>
+      <c r="L10" s="8">
+        <v>0.72550000000000003</v>
+      </c>
+      <c r="M10" s="5">
+        <v>7.1300000000000002E-2</v>
+      </c>
+      <c r="N10" s="8">
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="O10" s="5">
+        <v>5.9900000000000002E-2</v>
+      </c>
+      <c r="P10" s="5">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3">
         <v>0.68120000000000003</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C11" s="3">
         <v>7.4899999999999994E-2</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D11" s="3">
         <v>1.6E-2</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E11" s="3">
         <v>2.47E-2</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F11" s="3">
         <v>3.7100000000000001E-2</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G11" s="4">
         <v>0.69889999999999997</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H11" s="4">
         <v>7.1499999999999994E-2</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I11" s="4">
         <v>1.9800000000000002E-2</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J11" s="4">
         <v>2.86E-2</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K11" s="4">
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L11" s="5">
         <v>0.62560000000000004</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M11" s="5">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N11" s="5">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O11" s="5">
         <v>3.3099999999999997E-2</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P11" s="5">
         <v>3.5900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.74639999999999995</v>
+      </c>
+      <c r="C12" s="3">
+        <v>9.7900000000000001E-2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>4.8500000000000001E-2</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0.73980000000000001</v>
+      </c>
+      <c r="H12" s="4">
+        <v>8.43E-2</v>
+      </c>
+      <c r="I12" s="4">
+        <v>2.23E-2</v>
+      </c>
+      <c r="J12" s="4">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="K12" s="4">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0.71360000000000001</v>
+      </c>
+      <c r="M12" s="5">
+        <v>7.2099999999999997E-2</v>
+      </c>
+      <c r="N12" s="5">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="O12" s="8">
+        <v>6.0400000000000002E-2</v>
+      </c>
+      <c r="P12" s="8">
+        <v>6.5699999999999995E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1027,4 +1151,14 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21DE89CC-DA89-E849-8426-98934B0A771A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1171AF6F-87FE-014F-B8DE-197357667F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DBEB94-C6AD-2341-9CB9-11FA6BB612B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -136,6 +136,14 @@
   </si>
   <si>
     <t>sample_weight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GAT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GIN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -251,6 +259,7 @@
     <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -260,7 +269,6 @@
     <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -541,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R12"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -555,27 +563,27 @@
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="10" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="11" t="s">
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
       <c r="R1" s="2" t="s">
         <v>2</v>
       </c>
@@ -888,7 +896,7 @@
       <c r="P7" s="5">
         <v>6.54E-2</v>
       </c>
-      <c r="R7" s="12" t="s">
+      <c r="R7" s="9" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1140,6 +1148,106 @@
       </c>
       <c r="P12" s="8">
         <v>6.5699999999999995E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="D13" s="3">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="E13" s="3">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="H13" s="4">
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1.09E-2</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1.11E-2</v>
+      </c>
+      <c r="K13" s="4">
+        <v>1.61E-2</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0.62150000000000005</v>
+      </c>
+      <c r="M13" s="5">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="N13" s="5">
+        <v>2.5700000000000001E-2</v>
+      </c>
+      <c r="O13" s="5">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="P13" s="5">
+        <v>3.2800000000000003E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.66420000000000001</v>
+      </c>
+      <c r="C14" s="3">
+        <v>4.24E-2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1.23E-2</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2.0899999999999998E-2</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0.63639999999999997</v>
+      </c>
+      <c r="H14" s="4">
+        <v>2.8299999999999999E-2</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="J14" s="4">
+        <v>1.11E-2</v>
+      </c>
+      <c r="K14" s="4">
+        <v>1.5900000000000001E-2</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0.621</v>
+      </c>
+      <c r="M14" s="5">
+        <v>3.9800000000000002E-2</v>
+      </c>
+      <c r="N14" s="5">
+        <v>2.7400000000000001E-2</v>
+      </c>
+      <c r="O14" s="5">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="P14" s="5">
+        <v>3.6400000000000002E-2</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DBEB94-C6AD-2341-9CB9-11FA6BB612B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8525DC08-0BAD-9049-AF11-1F32E462FD9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -144,6 +144,10 @@
   </si>
   <si>
     <t>GIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Random</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -549,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -1248,6 +1252,56 @@
       </c>
       <c r="P14" s="5">
         <v>3.6400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.50019999999999998</v>
+      </c>
+      <c r="C15" s="3">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="E15" s="3">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.01E-2</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="4">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="I15" s="4">
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="J15" s="4">
+        <v>6.6E-3</v>
+      </c>
+      <c r="K15" s="4">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0.504</v>
+      </c>
+      <c r="M15" s="5">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="N15" s="5">
+        <v>1.84E-2</v>
+      </c>
+      <c r="O15" s="5">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="P15" s="5">
+        <v>1.9099999999999999E-2</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8525DC08-0BAD-9049-AF11-1F32E462FD9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2868F044-4838-5E41-8F41-88DFA522D072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -148,6 +148,18 @@
   </si>
   <si>
     <t>Random</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RGAT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EGC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GraphCL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -553,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -1054,254 +1066,404 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0.68120000000000003</v>
-      </c>
-      <c r="C11" s="3">
-        <v>7.4899999999999994E-2</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1.6E-2</v>
-      </c>
-      <c r="E11" s="3">
-        <v>2.47E-2</v>
-      </c>
-      <c r="F11" s="3">
-        <v>3.7100000000000001E-2</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0.69889999999999997</v>
-      </c>
-      <c r="H11" s="4">
-        <v>7.1499999999999994E-2</v>
-      </c>
-      <c r="I11" s="4">
-        <v>1.9800000000000002E-2</v>
-      </c>
-      <c r="J11" s="4">
-        <v>2.86E-2</v>
-      </c>
-      <c r="K11" s="4">
-        <v>4.0800000000000003E-2</v>
-      </c>
-      <c r="L11" s="5">
-        <v>0.62560000000000004</v>
-      </c>
-      <c r="M11" s="5">
-        <v>3.9399999999999998E-2</v>
-      </c>
-      <c r="N11" s="5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="O11" s="5">
-        <v>3.3099999999999997E-2</v>
-      </c>
-      <c r="P11" s="5">
-        <v>3.5900000000000001E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="3">
-        <v>0.74639999999999995</v>
-      </c>
-      <c r="C12" s="3">
-        <v>9.7900000000000001E-2</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1.9599999999999999E-2</v>
-      </c>
-      <c r="E12" s="3">
-        <v>3.2300000000000002E-2</v>
-      </c>
-      <c r="F12" s="3">
-        <v>4.8500000000000001E-2</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0.73980000000000001</v>
-      </c>
-      <c r="H12" s="4">
-        <v>8.43E-2</v>
-      </c>
-      <c r="I12" s="4">
-        <v>2.23E-2</v>
-      </c>
-      <c r="J12" s="4">
-        <v>3.3799999999999997E-2</v>
-      </c>
-      <c r="K12" s="4">
-        <v>4.8300000000000003E-2</v>
-      </c>
-      <c r="L12" s="5">
-        <v>0.71360000000000001</v>
-      </c>
-      <c r="M12" s="5">
-        <v>7.2099999999999997E-2</v>
-      </c>
-      <c r="N12" s="5">
-        <v>3.9699999999999999E-2</v>
-      </c>
-      <c r="O12" s="8">
-        <v>6.0400000000000002E-2</v>
-      </c>
-      <c r="P12" s="8">
-        <v>6.5699999999999995E-2</v>
-      </c>
-    </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B13" s="3">
-        <v>0.61499999999999999</v>
+        <v>0.50019999999999998</v>
       </c>
       <c r="C13" s="3">
-        <v>3.2199999999999999E-2</v>
+        <v>2.0500000000000001E-2</v>
       </c>
       <c r="D13" s="3">
-        <v>9.1999999999999998E-3</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="E13" s="3">
-        <v>8.6999999999999994E-3</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="F13" s="3">
-        <v>1.3599999999999999E-2</v>
+        <v>1.01E-2</v>
       </c>
       <c r="G13" s="4">
-        <v>0.60599999999999998</v>
+        <v>0.5</v>
       </c>
       <c r="H13" s="4">
-        <v>2.9600000000000001E-2</v>
+        <v>1.6400000000000001E-2</v>
       </c>
       <c r="I13" s="4">
-        <v>1.09E-2</v>
+        <v>8.0999999999999996E-3</v>
       </c>
       <c r="J13" s="4">
-        <v>1.11E-2</v>
+        <v>6.6E-3</v>
       </c>
       <c r="K13" s="4">
-        <v>1.61E-2</v>
+        <v>9.4000000000000004E-3</v>
       </c>
       <c r="L13" s="5">
-        <v>0.62150000000000005</v>
+        <v>0.504</v>
       </c>
       <c r="M13" s="5">
-        <v>3.9399999999999998E-2</v>
+        <v>2.1100000000000001E-2</v>
       </c>
       <c r="N13" s="5">
-        <v>2.5700000000000001E-2</v>
+        <v>1.84E-2</v>
       </c>
       <c r="O13" s="5">
-        <v>2.8500000000000001E-2</v>
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="P13" s="5">
-        <v>3.2800000000000003E-2</v>
+        <v>1.9099999999999999E-2</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14" s="3">
-        <v>0.66420000000000001</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="C14" s="3">
-        <v>4.24E-2</v>
+        <v>3.2199999999999999E-2</v>
       </c>
       <c r="D14" s="3">
-        <v>1.23E-2</v>
+        <v>9.1999999999999998E-3</v>
       </c>
       <c r="E14" s="3">
-        <v>1.3899999999999999E-2</v>
+        <v>8.6999999999999994E-3</v>
       </c>
       <c r="F14" s="3">
-        <v>2.0899999999999998E-2</v>
+        <v>1.3599999999999999E-2</v>
       </c>
       <c r="G14" s="4">
-        <v>0.63639999999999997</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="H14" s="4">
-        <v>2.8299999999999999E-2</v>
+        <v>2.9600000000000001E-2</v>
       </c>
       <c r="I14" s="4">
-        <v>1.2699999999999999E-2</v>
+        <v>1.09E-2</v>
       </c>
       <c r="J14" s="4">
         <v>1.11E-2</v>
       </c>
       <c r="K14" s="4">
-        <v>1.5900000000000001E-2</v>
+        <v>1.61E-2</v>
       </c>
       <c r="L14" s="5">
-        <v>0.621</v>
+        <v>0.62150000000000005</v>
       </c>
       <c r="M14" s="5">
-        <v>3.9800000000000002E-2</v>
+        <v>3.9399999999999998E-2</v>
       </c>
       <c r="N14" s="5">
-        <v>2.7400000000000001E-2</v>
+        <v>2.5700000000000001E-2</v>
       </c>
       <c r="O14" s="5">
-        <v>3.3599999999999998E-2</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="P14" s="5">
-        <v>3.6400000000000002E-2</v>
+        <v>3.2800000000000003E-2</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="3">
-        <v>0.50019999999999998</v>
+        <v>0.67200000000000004</v>
       </c>
       <c r="C15" s="3">
+        <v>5.3699999999999998E-2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.77E-2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.64049999999999996</v>
+      </c>
+      <c r="H15" s="4">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1.35E-2</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1.44E-2</v>
+      </c>
+      <c r="K15" s="4">
+        <v>2.06E-2</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0.63139999999999996</v>
+      </c>
+      <c r="M15" s="5">
+        <v>4.9500000000000002E-2</v>
+      </c>
+      <c r="N15" s="5">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="O15" s="5">
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="P15" s="5">
+        <v>4.53E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.67730000000000001</v>
+      </c>
+      <c r="C16" s="3">
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.67310000000000003</v>
+      </c>
+      <c r="H16" s="4">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="K16" s="4">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0.68069999999999997</v>
+      </c>
+      <c r="M16" s="5">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="N16" s="5">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="O16" s="5">
+        <v>4.58E-2</v>
+      </c>
+      <c r="P16" s="5">
+        <v>5.0799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0.67020000000000002</v>
+      </c>
+      <c r="C17" s="3">
+        <v>4.4499999999999998E-2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0.67569999999999997</v>
+      </c>
+      <c r="H17" s="4">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="J17" s="4">
         <v>2.0500000000000001E-2</v>
       </c>
-      <c r="D15" s="3">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="E15" s="3">
-        <v>6.7000000000000002E-3</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1.01E-2</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="H15" s="4">
-        <v>1.6400000000000001E-2</v>
-      </c>
-      <c r="I15" s="4">
-        <v>8.0999999999999996E-3</v>
-      </c>
-      <c r="J15" s="4">
-        <v>6.6E-3</v>
-      </c>
-      <c r="K15" s="4">
-        <v>9.4000000000000004E-3</v>
-      </c>
-      <c r="L15" s="5">
-        <v>0.504</v>
-      </c>
-      <c r="M15" s="5">
-        <v>2.1100000000000001E-2</v>
-      </c>
-      <c r="N15" s="5">
-        <v>1.84E-2</v>
-      </c>
-      <c r="O15" s="5">
-        <v>1.7399999999999999E-2</v>
-      </c>
-      <c r="P15" s="5">
-        <v>1.9099999999999999E-2</v>
+      <c r="K17" s="4">
+        <v>2.92E-2</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="M17" s="5">
+        <v>5.96E-2</v>
+      </c>
+      <c r="N17" s="5">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="O17" s="5">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="P17" s="5">
+        <v>5.2400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0.65910000000000002</v>
+      </c>
+      <c r="C18" s="3">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1.2E-2</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1.44E-2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0.63759999999999994</v>
+      </c>
+      <c r="H18" s="4">
+        <v>4.19E-2</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="J18" s="4">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="K18" s="4">
+        <v>2.1399999999999999E-2</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="M18" s="5">
+        <v>6.25E-2</v>
+      </c>
+      <c r="N18" s="5">
+        <v>3.0599999999999999E-2</v>
+      </c>
+      <c r="O18" s="5">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="P18" s="5">
+        <v>5.4899999999999997E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.68120000000000003</v>
+      </c>
+      <c r="C19" s="3">
+        <v>7.4899999999999994E-2</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2.47E-2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0.69889999999999997</v>
+      </c>
+      <c r="H19" s="4">
+        <v>7.1499999999999994E-2</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="J19" s="4">
+        <v>2.86E-2</v>
+      </c>
+      <c r="K19" s="4">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0.62560000000000004</v>
+      </c>
+      <c r="M19" s="5">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="N19" s="5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O19" s="5">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="P19" s="5">
+        <v>3.5900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0.74639999999999995</v>
+      </c>
+      <c r="C20" s="3">
+        <v>9.7900000000000001E-2</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="E20" s="3">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="F20" s="3">
+        <v>4.8500000000000001E-2</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0.73980000000000001</v>
+      </c>
+      <c r="H20" s="4">
+        <v>8.43E-2</v>
+      </c>
+      <c r="I20" s="4">
+        <v>2.23E-2</v>
+      </c>
+      <c r="J20" s="4">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="K20" s="4">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0.71360000000000001</v>
+      </c>
+      <c r="M20" s="5">
+        <v>7.2099999999999997E-2</v>
+      </c>
+      <c r="N20" s="5">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="O20" s="8">
+        <v>6.0400000000000002E-2</v>
+      </c>
+      <c r="P20" s="8">
+        <v>6.5699999999999995E-2</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2868F044-4838-5E41-8F41-88DFA522D072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C14D47A-01C1-F447-BEA6-320100DFAE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -60,21 +60,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>MMOE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-      </rPr>
-      <t>架构</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Data</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -160,6 +145,14 @@
   </si>
   <si>
     <t>GraphCL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMOE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CMR_GNN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -170,7 +163,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,18 +194,12 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="SimSun"/>
       <family val="1"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -234,6 +221,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -265,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -275,7 +268,7 @@
     <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -285,6 +278,7 @@
     <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -565,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -577,24 +571,24 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
       <c r="G1" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H1" s="11"/>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
@@ -659,7 +653,7 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3">
         <v>0.75229999999999997</v>
@@ -709,7 +703,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="3">
         <v>0.75170000000000003</v>
@@ -757,12 +751,12 @@
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="3">
         <v>0.75249999999999995</v>
@@ -810,12 +804,12 @@
         <v>6.1199999999999997E-2</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="18" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="6">
         <v>0.754</v>
@@ -864,606 +858,658 @@
       </c>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0.75070000000000003</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.11070000000000001</v>
-      </c>
-      <c r="D7" s="3">
-        <v>2.06E-2</v>
-      </c>
-      <c r="E7" s="6">
-        <v>3.6499999999999998E-2</v>
-      </c>
-      <c r="F7" s="6">
-        <v>5.4800000000000001E-2</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0.74750000000000005</v>
-      </c>
-      <c r="H7" s="4">
-        <v>8.9399999999999993E-2</v>
-      </c>
-      <c r="I7" s="7">
-        <v>2.41E-2</v>
-      </c>
-      <c r="J7" s="4">
-        <v>3.5900000000000001E-2</v>
-      </c>
-      <c r="K7" s="4">
-        <v>5.1299999999999998E-2</v>
-      </c>
-      <c r="L7" s="5">
-        <v>0.72130000000000005</v>
-      </c>
-      <c r="M7" s="5">
-        <v>7.1499999999999994E-2</v>
-      </c>
-      <c r="N7" s="5">
-        <v>4.0599999999999997E-2</v>
-      </c>
-      <c r="O7" s="8">
-        <v>6.0400000000000002E-2</v>
-      </c>
-      <c r="P7" s="5">
-        <v>6.54E-2</v>
-      </c>
       <c r="R7" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0.74770000000000003</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.10340000000000001</v>
-      </c>
-      <c r="D8" s="3">
-        <v>2.0400000000000001E-2</v>
-      </c>
-      <c r="E8" s="3">
-        <v>3.4099999999999998E-2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>5.1299999999999998E-2</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0.74709999999999999</v>
-      </c>
-      <c r="H8" s="7">
-        <v>9.1499999999999998E-2</v>
-      </c>
-      <c r="I8" s="4">
-        <v>2.3800000000000002E-2</v>
-      </c>
-      <c r="J8" s="7">
-        <v>3.6700000000000003E-2</v>
-      </c>
-      <c r="K8" s="7">
-        <v>5.2400000000000002E-2</v>
-      </c>
-      <c r="L8" s="5">
-        <v>0.71550000000000002</v>
-      </c>
-      <c r="M8" s="5">
-        <v>6.9099999999999995E-2</v>
-      </c>
-      <c r="N8" s="5">
-        <v>4.0500000000000001E-2</v>
-      </c>
-      <c r="O8" s="5">
-        <v>5.8099999999999999E-2</v>
-      </c>
-      <c r="P8" s="5">
-        <v>6.3100000000000003E-2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B9" s="3">
-        <v>0.74580000000000002</v>
-      </c>
-      <c r="C9" s="3">
-        <v>9.6299999999999997E-2</v>
+        <v>0.75070000000000003</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.11070000000000001</v>
       </c>
       <c r="D9" s="3">
-        <v>1.9900000000000001E-2</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3.1800000000000002E-2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>4.7800000000000002E-2</v>
+        <v>2.06E-2</v>
+      </c>
+      <c r="E9" s="6">
+        <v>3.6499999999999998E-2</v>
+      </c>
+      <c r="F9" s="6">
+        <v>5.4800000000000001E-2</v>
       </c>
       <c r="G9" s="4">
-        <v>0.73829999999999996</v>
+        <v>0.74750000000000005</v>
       </c>
       <c r="H9" s="4">
-        <v>8.3699999999999997E-2</v>
-      </c>
-      <c r="I9" s="4">
-        <v>2.2599999999999999E-2</v>
+        <v>8.9399999999999993E-2</v>
+      </c>
+      <c r="I9" s="7">
+        <v>2.41E-2</v>
       </c>
       <c r="J9" s="4">
-        <v>3.3599999999999998E-2</v>
+        <v>3.5900000000000001E-2</v>
       </c>
       <c r="K9" s="4">
-        <v>4.7899999999999998E-2</v>
+        <v>5.1299999999999998E-2</v>
       </c>
       <c r="L9" s="5">
-        <v>0.71079999999999999</v>
+        <v>0.72130000000000005</v>
       </c>
       <c r="M9" s="5">
-        <v>5.96E-2</v>
+        <v>7.1499999999999994E-2</v>
       </c>
       <c r="N9" s="5">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="O9" s="5">
-        <v>4.8599999999999997E-2</v>
+        <v>4.0599999999999997E-2</v>
+      </c>
+      <c r="O9" s="8">
+        <v>6.0400000000000002E-2</v>
       </c>
       <c r="P9" s="5">
-        <v>5.3499999999999999E-2</v>
+        <v>6.54E-2</v>
       </c>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B10" s="3">
+        <v>0.74770000000000003</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.10340000000000001</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.0400000000000001E-2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.74709999999999999</v>
+      </c>
+      <c r="H10" s="7">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="I10" s="4">
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="J10" s="7">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="K10" s="7">
+        <v>5.2400000000000002E-2</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0.71550000000000002</v>
+      </c>
+      <c r="M10" s="5">
+        <v>6.9099999999999995E-2</v>
+      </c>
+      <c r="N10" s="5">
+        <v>4.0500000000000001E-2</v>
+      </c>
+      <c r="O10" s="5">
+        <v>5.8099999999999999E-2</v>
+      </c>
+      <c r="P10" s="5">
+        <v>6.3100000000000003E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.74580000000000002</v>
+      </c>
+      <c r="C11" s="3">
+        <v>9.6299999999999997E-2</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="E11" s="3">
+        <v>3.1800000000000002E-2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0.73829999999999996</v>
+      </c>
+      <c r="H11" s="4">
+        <v>8.3699999999999997E-2</v>
+      </c>
+      <c r="I11" s="4">
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="J11" s="4">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="K11" s="4">
+        <v>4.7899999999999998E-2</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0.71079999999999999</v>
+      </c>
+      <c r="M11" s="5">
+        <v>5.96E-2</v>
+      </c>
+      <c r="N11" s="5">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="O11" s="5">
+        <v>4.8599999999999997E-2</v>
+      </c>
+      <c r="P11" s="5">
+        <v>5.3499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="3">
         <v>7.4709999999999999E-2</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C12" s="3">
         <v>9.6000000000000002E-2</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D12" s="3">
         <v>1.9699999999999999E-2</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E12" s="3">
         <v>3.1699999999999999E-2</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F12" s="3">
         <v>4.7600000000000003E-2</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G12" s="4">
         <v>0.74260000000000004</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H12" s="4">
         <v>7.9899999999999999E-2</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I12" s="4">
         <v>2.2100000000000002E-2</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J12" s="4">
         <v>3.2099999999999997E-2</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K12" s="4">
         <v>4.58E-2</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L12" s="8">
         <v>0.72550000000000003</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M12" s="5">
         <v>7.1300000000000002E-2</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N12" s="8">
         <v>4.1799999999999997E-2</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O12" s="5">
         <v>5.9900000000000002E-2</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P12" s="5">
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="1" t="s">
+    <row r="14" spans="1:18">
+      <c r="A14" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.50019999999999998</v>
+      </c>
+      <c r="C14" s="3">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1.01E-2</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="4">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="I14" s="4">
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="J14" s="4">
+        <v>6.6E-3</v>
+      </c>
+      <c r="K14" s="4">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0.504</v>
+      </c>
+      <c r="M14" s="5">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1.84E-2</v>
+      </c>
+      <c r="O14" s="5">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="P14" s="5">
+        <v>1.9099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="3">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="E15" s="3">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="H15" s="4">
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1.09E-2</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1.11E-2</v>
+      </c>
+      <c r="K15" s="4">
+        <v>1.61E-2</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0.62150000000000005</v>
+      </c>
+      <c r="M15" s="5">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="N15" s="5">
+        <v>2.5700000000000001E-2</v>
+      </c>
+      <c r="O15" s="5">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="P15" s="5">
+        <v>3.2800000000000003E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="3">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="C16" s="3">
+        <v>5.3699999999999998E-2</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1.77E-2</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0.64049999999999996</v>
+      </c>
+      <c r="H16" s="4">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1.35E-2</v>
+      </c>
+      <c r="J16" s="4">
+        <v>1.44E-2</v>
+      </c>
+      <c r="K16" s="4">
+        <v>2.06E-2</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0.63139999999999996</v>
+      </c>
+      <c r="M16" s="5">
+        <v>4.9500000000000002E-2</v>
+      </c>
+      <c r="N16" s="5">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="O16" s="5">
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="P16" s="5">
+        <v>4.53E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="3">
-        <v>0.50019999999999998</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="B17" s="3">
+        <v>0.67730000000000001</v>
+      </c>
+      <c r="C17" s="3">
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0.67310000000000003</v>
+      </c>
+      <c r="H17" s="4">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="J17" s="4">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="K17" s="4">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0.68069999999999997</v>
+      </c>
+      <c r="M17" s="5">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="N17" s="5">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="O17" s="5">
+        <v>4.58E-2</v>
+      </c>
+      <c r="P17" s="5">
+        <v>5.0799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0.67020000000000002</v>
+      </c>
+      <c r="C18" s="3">
+        <v>4.4499999999999998E-2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0.67569999999999997</v>
+      </c>
+      <c r="H18" s="4">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="J18" s="4">
         <v>2.0500000000000001E-2</v>
       </c>
-      <c r="D13" s="3">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="E13" s="3">
-        <v>6.7000000000000002E-3</v>
-      </c>
-      <c r="F13" s="3">
-        <v>1.01E-2</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="H13" s="4">
-        <v>1.6400000000000001E-2</v>
-      </c>
-      <c r="I13" s="4">
-        <v>8.0999999999999996E-3</v>
-      </c>
-      <c r="J13" s="4">
-        <v>6.6E-3</v>
-      </c>
-      <c r="K13" s="4">
-        <v>9.4000000000000004E-3</v>
-      </c>
-      <c r="L13" s="5">
-        <v>0.504</v>
-      </c>
-      <c r="M13" s="5">
-        <v>2.1100000000000001E-2</v>
-      </c>
-      <c r="N13" s="5">
-        <v>1.84E-2</v>
-      </c>
-      <c r="O13" s="5">
-        <v>1.7399999999999999E-2</v>
-      </c>
-      <c r="P13" s="5">
-        <v>1.9099999999999999E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="3">
-        <v>0.61499999999999999</v>
-      </c>
-      <c r="C14" s="3">
-        <v>3.2199999999999999E-2</v>
-      </c>
-      <c r="D14" s="3">
-        <v>9.1999999999999998E-3</v>
-      </c>
-      <c r="E14" s="3">
-        <v>8.6999999999999994E-3</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1.3599999999999999E-2</v>
-      </c>
-      <c r="G14" s="4">
-        <v>0.60599999999999998</v>
-      </c>
-      <c r="H14" s="4">
-        <v>2.9600000000000001E-2</v>
-      </c>
-      <c r="I14" s="4">
-        <v>1.09E-2</v>
-      </c>
-      <c r="J14" s="4">
-        <v>1.11E-2</v>
-      </c>
-      <c r="K14" s="4">
-        <v>1.61E-2</v>
-      </c>
-      <c r="L14" s="5">
-        <v>0.62150000000000005</v>
-      </c>
-      <c r="M14" s="5">
+      <c r="K18" s="4">
+        <v>2.92E-2</v>
+      </c>
+      <c r="L18" s="5">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="M18" s="5">
+        <v>5.96E-2</v>
+      </c>
+      <c r="N18" s="5">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="O18" s="5">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="P18" s="5">
+        <v>5.2400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.65910000000000002</v>
+      </c>
+      <c r="C19" s="3">
+        <v>4.4200000000000003E-2</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1.2E-2</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1.44E-2</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0.63759999999999994</v>
+      </c>
+      <c r="H19" s="4">
+        <v>4.19E-2</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="J19" s="4">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="K19" s="4">
+        <v>2.1399999999999999E-2</v>
+      </c>
+      <c r="L19" s="5">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="M19" s="5">
+        <v>6.25E-2</v>
+      </c>
+      <c r="N19" s="5">
+        <v>3.0599999999999999E-2</v>
+      </c>
+      <c r="O19" s="5">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="P19" s="5">
+        <v>5.4899999999999997E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0.68120000000000003</v>
+      </c>
+      <c r="C20" s="3">
+        <v>7.4899999999999994E-2</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2.47E-2</v>
+      </c>
+      <c r="F20" s="3">
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0.69889999999999997</v>
+      </c>
+      <c r="H20" s="4">
+        <v>7.1499999999999994E-2</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="J20" s="4">
+        <v>2.86E-2</v>
+      </c>
+      <c r="K20" s="4">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="L20" s="5">
+        <v>0.62560000000000004</v>
+      </c>
+      <c r="M20" s="5">
         <v>3.9399999999999998E-2</v>
       </c>
-      <c r="N14" s="5">
-        <v>2.5700000000000001E-2</v>
-      </c>
-      <c r="O14" s="5">
-        <v>2.8500000000000001E-2</v>
-      </c>
-      <c r="P14" s="5">
-        <v>3.2800000000000003E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="3">
-        <v>0.67200000000000004</v>
-      </c>
-      <c r="C15" s="3">
-        <v>5.3699999999999998E-2</v>
-      </c>
-      <c r="D15" s="3">
-        <v>1.3599999999999999E-2</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1.77E-2</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2.6599999999999999E-2</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0.64049999999999996</v>
-      </c>
-      <c r="H15" s="4">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="I15" s="4">
-        <v>1.35E-2</v>
-      </c>
-      <c r="J15" s="4">
-        <v>1.44E-2</v>
-      </c>
-      <c r="K15" s="4">
+      <c r="N20" s="5">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="O20" s="5">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="P20" s="5">
+        <v>3.5900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.74639999999999995</v>
+      </c>
+      <c r="C21" s="3">
+        <v>9.7900000000000001E-2</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="F21" s="3">
+        <v>4.8500000000000001E-2</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0.73980000000000001</v>
+      </c>
+      <c r="H21" s="4">
+        <v>8.43E-2</v>
+      </c>
+      <c r="I21" s="4">
+        <v>2.23E-2</v>
+      </c>
+      <c r="J21" s="4">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="K21" s="4">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="L21" s="5">
+        <v>0.71360000000000001</v>
+      </c>
+      <c r="M21" s="5">
+        <v>7.2099999999999997E-2</v>
+      </c>
+      <c r="N21" s="5">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="O21" s="8">
+        <v>6.0400000000000002E-2</v>
+      </c>
+      <c r="P21" s="8">
+        <v>6.5699999999999995E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0.68169999999999997</v>
+      </c>
+      <c r="C22" s="3">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2.01E-2</v>
+      </c>
+      <c r="F22" s="3">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0.72240000000000004</v>
+      </c>
+      <c r="H22" s="4">
+        <v>7.0300000000000001E-2</v>
+      </c>
+      <c r="I22" s="4">
         <v>2.06E-2</v>
       </c>
-      <c r="L15" s="5">
-        <v>0.63139999999999996</v>
-      </c>
-      <c r="M15" s="5">
-        <v>4.9500000000000002E-2</v>
-      </c>
-      <c r="N15" s="5">
-        <v>3.1199999999999999E-2</v>
-      </c>
-      <c r="O15" s="5">
-        <v>4.1799999999999997E-2</v>
-      </c>
-      <c r="P15" s="5">
-        <v>4.53E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="3">
-        <v>0.67730000000000001</v>
-      </c>
-      <c r="C16" s="3">
-        <v>5.3400000000000003E-2</v>
-      </c>
-      <c r="D16" s="3">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="E16" s="3">
-        <v>1.6899999999999998E-2</v>
-      </c>
-      <c r="F16" s="3">
-        <v>2.5600000000000001E-2</v>
-      </c>
-      <c r="G16" s="4">
-        <v>0.67310000000000003</v>
-      </c>
-      <c r="H16" s="4">
-        <v>5.0500000000000003E-2</v>
-      </c>
-      <c r="I16" s="4">
-        <v>1.4800000000000001E-2</v>
-      </c>
-      <c r="J16" s="4">
-        <v>1.9599999999999999E-2</v>
-      </c>
-      <c r="K16" s="4">
+      <c r="J22" s="4">
         <v>2.8199999999999999E-2</v>
       </c>
-      <c r="L16" s="5">
-        <v>0.68069999999999997</v>
-      </c>
-      <c r="M16" s="5">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="N16" s="5">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="O16" s="5">
-        <v>4.58E-2</v>
-      </c>
-      <c r="P16" s="5">
-        <v>5.0799999999999998E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="3">
-        <v>0.67020000000000002</v>
-      </c>
-      <c r="C17" s="3">
-        <v>4.4499999999999998E-2</v>
-      </c>
-      <c r="D17" s="3">
-        <v>1.1900000000000001E-2</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1.4200000000000001E-2</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2.1499999999999998E-2</v>
-      </c>
-      <c r="G17" s="4">
-        <v>0.67569999999999997</v>
-      </c>
-      <c r="H17" s="4">
-        <v>5.1200000000000002E-2</v>
-      </c>
-      <c r="I17" s="4">
-        <v>1.5299999999999999E-2</v>
-      </c>
-      <c r="J17" s="4">
-        <v>2.0500000000000001E-2</v>
-      </c>
-      <c r="K17" s="4">
-        <v>2.92E-2</v>
-      </c>
-      <c r="L17" s="5">
-        <v>0.67300000000000004</v>
-      </c>
-      <c r="M17" s="5">
-        <v>5.96E-2</v>
-      </c>
-      <c r="N17" s="5">
-        <v>3.4200000000000001E-2</v>
-      </c>
-      <c r="O17" s="5">
-        <v>4.6899999999999997E-2</v>
-      </c>
-      <c r="P17" s="5">
-        <v>5.2400000000000002E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="3">
-        <v>0.65910000000000002</v>
-      </c>
-      <c r="C18" s="3">
-        <v>4.4200000000000003E-2</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1.2E-2</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1.44E-2</v>
-      </c>
-      <c r="F18" s="3">
-        <v>2.1700000000000001E-2</v>
-      </c>
-      <c r="G18" s="4">
-        <v>0.63759999999999994</v>
-      </c>
-      <c r="H18" s="4">
-        <v>4.19E-2</v>
-      </c>
-      <c r="I18" s="4">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="J18" s="4">
-        <v>1.4500000000000001E-2</v>
-      </c>
-      <c r="K18" s="4">
-        <v>2.1399999999999999E-2</v>
-      </c>
-      <c r="L18" s="5">
-        <v>0.67400000000000004</v>
-      </c>
-      <c r="M18" s="5">
-        <v>6.25E-2</v>
-      </c>
-      <c r="N18" s="5">
-        <v>3.0599999999999999E-2</v>
-      </c>
-      <c r="O18" s="5">
-        <v>4.9099999999999998E-2</v>
-      </c>
-      <c r="P18" s="5">
-        <v>5.4899999999999997E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="3">
-        <v>0.68120000000000003</v>
-      </c>
-      <c r="C19" s="3">
-        <v>7.4899999999999994E-2</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1.6E-2</v>
-      </c>
-      <c r="E19" s="3">
-        <v>2.47E-2</v>
-      </c>
-      <c r="F19" s="3">
-        <v>3.7100000000000001E-2</v>
-      </c>
-      <c r="G19" s="4">
-        <v>0.69889999999999997</v>
-      </c>
-      <c r="H19" s="4">
-        <v>7.1499999999999994E-2</v>
-      </c>
-      <c r="I19" s="4">
-        <v>1.9800000000000002E-2</v>
-      </c>
-      <c r="J19" s="4">
-        <v>2.86E-2</v>
-      </c>
-      <c r="K19" s="4">
-        <v>4.0800000000000003E-2</v>
-      </c>
-      <c r="L19" s="5">
-        <v>0.62560000000000004</v>
-      </c>
-      <c r="M19" s="5">
-        <v>3.9399999999999998E-2</v>
-      </c>
-      <c r="N19" s="5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="O19" s="5">
-        <v>3.3099999999999997E-2</v>
-      </c>
-      <c r="P19" s="5">
-        <v>3.5900000000000001E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="3">
-        <v>0.74639999999999995</v>
-      </c>
-      <c r="C20" s="3">
-        <v>9.7900000000000001E-2</v>
-      </c>
-      <c r="D20" s="3">
-        <v>1.9599999999999999E-2</v>
-      </c>
-      <c r="E20" s="3">
-        <v>3.2300000000000002E-2</v>
-      </c>
-      <c r="F20" s="3">
-        <v>4.8500000000000001E-2</v>
-      </c>
-      <c r="G20" s="4">
-        <v>0.73980000000000001</v>
-      </c>
-      <c r="H20" s="4">
-        <v>8.43E-2</v>
-      </c>
-      <c r="I20" s="4">
-        <v>2.23E-2</v>
-      </c>
-      <c r="J20" s="4">
-        <v>3.3799999999999997E-2</v>
-      </c>
-      <c r="K20" s="4">
-        <v>4.8300000000000003E-2</v>
-      </c>
-      <c r="L20" s="5">
-        <v>0.71360000000000001</v>
-      </c>
-      <c r="M20" s="5">
-        <v>7.2099999999999997E-2</v>
-      </c>
-      <c r="N20" s="5">
-        <v>3.9699999999999999E-2</v>
-      </c>
-      <c r="O20" s="8">
-        <v>6.0400000000000002E-2</v>
-      </c>
-      <c r="P20" s="8">
-        <v>6.5699999999999995E-2</v>
+      <c r="K22" s="4">
+        <v>4.02E-2</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0.63149999999999995</v>
+      </c>
+      <c r="M22" s="5">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="N22" s="5">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="O22" s="5">
+        <v>2.81E-2</v>
+      </c>
+      <c r="P22" s="5">
+        <v>3.15E-2</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C14D47A-01C1-F447-BEA6-320100DFAE4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73CF95B7-0B1F-B048-84F2-90BB97773B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31760" yWindow="-6400" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="44">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -76,10 +76,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Full_ClaOth_Reg=1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Full_ClaOth_Reg=1e-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -153,6 +149,175 @@
   </si>
   <si>
     <t>CMR_GNN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Full_ClaOthBest</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Ablation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>需要将整个组件移除</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reg=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Full_ClaOthBest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>0.01</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reg=0.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reg=0.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三线图*5（3数据=3颜色，4节）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sensitive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ablation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Full_ClaOthBest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>64</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hdim=32</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Full_ClaOthBest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>128</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Full_ClaOthBest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（96）</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -258,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -279,6 +444,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -559,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -574,21 +740,21 @@
         <v>8</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
       <c r="F1" s="10"/>
       <c r="G1" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H1" s="11"/>
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M1" s="12"/>
       <c r="N1" s="12"/>
@@ -651,59 +817,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0.75229999999999997</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0.1023</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2.06E-2</v>
-      </c>
-      <c r="E3" s="3">
-        <v>3.3700000000000001E-2</v>
-      </c>
-      <c r="F3" s="3">
-        <v>5.0599999999999999E-2</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0.749</v>
-      </c>
-      <c r="H3" s="4">
-        <v>8.9599999999999999E-2</v>
-      </c>
-      <c r="I3" s="4">
-        <v>2.3599999999999999E-2</v>
-      </c>
-      <c r="J3" s="4">
-        <v>3.5900000000000001E-2</v>
-      </c>
-      <c r="K3" s="4">
-        <v>5.1299999999999998E-2</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0.72460000000000002</v>
-      </c>
-      <c r="M3" s="8">
-        <v>7.22E-2</v>
-      </c>
-      <c r="N3" s="5">
-        <v>4.1200000000000001E-2</v>
-      </c>
-      <c r="O3" s="8">
-        <v>6.0400000000000002E-2</v>
-      </c>
-      <c r="P3" s="8">
-        <v>6.5699999999999995E-2</v>
-      </c>
-    </row>
     <row r="4" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3">
         <v>0.75170000000000003</v>
@@ -804,712 +920,1232 @@
         <v>6.1199999999999997E-2</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="18" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="6">
-        <v>0.754</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0.10340000000000001</v>
-      </c>
-      <c r="D6" s="6">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="E6" s="3">
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="F6" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
+      <c r="R6" s="9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.50019999999999998</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1.01E-2</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="I9" s="4">
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="J9" s="4">
+        <v>6.6E-3</v>
+      </c>
+      <c r="K9" s="4">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="L9" s="5">
+        <v>0.504</v>
+      </c>
+      <c r="M9" s="5">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1.84E-2</v>
+      </c>
+      <c r="O9" s="5">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="P9" s="5">
+        <v>1.9099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="E10" s="3">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="H10" s="4">
+        <v>2.9600000000000001E-2</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1.09E-2</v>
+      </c>
+      <c r="J10" s="4">
+        <v>1.11E-2</v>
+      </c>
+      <c r="K10" s="4">
+        <v>1.61E-2</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0.62150000000000005</v>
+      </c>
+      <c r="M10" s="5">
+        <v>3.9399999999999998E-2</v>
+      </c>
+      <c r="N10" s="5">
+        <v>2.5700000000000001E-2</v>
+      </c>
+      <c r="O10" s="5">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="P10" s="5">
+        <v>3.2800000000000003E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="C11" s="3">
+        <v>5.3699999999999998E-2</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1.77E-2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0.64049999999999996</v>
+      </c>
+      <c r="H11" s="4">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1.35E-2</v>
+      </c>
+      <c r="J11" s="4">
+        <v>1.44E-2</v>
+      </c>
+      <c r="K11" s="4">
+        <v>2.06E-2</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0.63139999999999996</v>
+      </c>
+      <c r="M11" s="5">
+        <v>4.9500000000000002E-2</v>
+      </c>
+      <c r="N11" s="5">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="O11" s="5">
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="P11" s="5">
+        <v>4.53E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.67730000000000001</v>
+      </c>
+      <c r="C12" s="3">
+        <v>5.3400000000000003E-2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="F12" s="3">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0.67310000000000003</v>
+      </c>
+      <c r="H12" s="4">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="K12" s="4">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0.68069999999999997</v>
+      </c>
+      <c r="M12" s="5">
+        <v>5.7500000000000002E-2</v>
+      </c>
+      <c r="N12" s="5">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="O12" s="5">
+        <v>4.58E-2</v>
+      </c>
+      <c r="P12" s="5">
+        <v>5.0799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.67020000000000002</v>
+      </c>
+      <c r="C13" s="3">
+        <v>4.4499999999999998E-2</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0.67569999999999997</v>
+      </c>
+      <c r="H13" s="4">
         <v>5.1200000000000002E-2</v>
       </c>
-      <c r="G6" s="7">
-        <v>0.75</v>
-      </c>
-      <c r="H6" s="4">
-        <v>8.9099999999999999E-2</v>
-      </c>
-      <c r="I6" s="4">
-        <v>2.3800000000000002E-2</v>
-      </c>
-      <c r="J6" s="4">
-        <v>3.5799999999999998E-2</v>
-      </c>
-      <c r="K6" s="4">
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0.72050000000000003</v>
-      </c>
-      <c r="M6" s="5">
-        <v>6.3399999999999998E-2</v>
-      </c>
-      <c r="N6" s="5">
-        <v>4.0300000000000002E-2</v>
-      </c>
-      <c r="O6" s="5">
-        <v>5.2900000000000003E-2</v>
-      </c>
-      <c r="P6" s="5">
-        <v>5.7599999999999998E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="R7" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0.75070000000000003</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.11070000000000001</v>
-      </c>
-      <c r="D9" s="3">
-        <v>2.06E-2</v>
-      </c>
-      <c r="E9" s="6">
-        <v>3.6499999999999998E-2</v>
-      </c>
-      <c r="F9" s="6">
-        <v>5.4800000000000001E-2</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.74750000000000005</v>
-      </c>
-      <c r="H9" s="4">
-        <v>8.9399999999999993E-2</v>
-      </c>
-      <c r="I9" s="7">
-        <v>2.41E-2</v>
-      </c>
-      <c r="J9" s="4">
-        <v>3.5900000000000001E-2</v>
-      </c>
-      <c r="K9" s="4">
-        <v>5.1299999999999998E-2</v>
-      </c>
-      <c r="L9" s="5">
-        <v>0.72130000000000005</v>
-      </c>
-      <c r="M9" s="5">
-        <v>7.1499999999999994E-2</v>
-      </c>
-      <c r="N9" s="5">
-        <v>4.0599999999999997E-2</v>
-      </c>
-      <c r="O9" s="8">
-        <v>6.0400000000000002E-2</v>
-      </c>
-      <c r="P9" s="5">
-        <v>6.54E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="3">
-        <v>0.74770000000000003</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0.10340000000000001</v>
-      </c>
-      <c r="D10" s="3">
-        <v>2.0400000000000001E-2</v>
-      </c>
-      <c r="E10" s="3">
-        <v>3.4099999999999998E-2</v>
-      </c>
-      <c r="F10" s="3">
-        <v>5.1299999999999998E-2</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0.74709999999999999</v>
-      </c>
-      <c r="H10" s="7">
-        <v>9.1499999999999998E-2</v>
-      </c>
-      <c r="I10" s="4">
-        <v>2.3800000000000002E-2</v>
-      </c>
-      <c r="J10" s="7">
-        <v>3.6700000000000003E-2</v>
-      </c>
-      <c r="K10" s="7">
+      <c r="I13" s="4">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="J13" s="4">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="K13" s="4">
+        <v>2.92E-2</v>
+      </c>
+      <c r="L13" s="5">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="M13" s="5">
+        <v>5.96E-2</v>
+      </c>
+      <c r="N13" s="5">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="O13" s="5">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="P13" s="5">
         <v>5.2400000000000002E-2</v>
-      </c>
-      <c r="L10" s="5">
-        <v>0.71550000000000002</v>
-      </c>
-      <c r="M10" s="5">
-        <v>6.9099999999999995E-2</v>
-      </c>
-      <c r="N10" s="5">
-        <v>4.0500000000000001E-2</v>
-      </c>
-      <c r="O10" s="5">
-        <v>5.8099999999999999E-2</v>
-      </c>
-      <c r="P10" s="5">
-        <v>6.3100000000000003E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="3">
-        <v>0.74580000000000002</v>
-      </c>
-      <c r="C11" s="3">
-        <v>9.6299999999999997E-2</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1.9900000000000001E-2</v>
-      </c>
-      <c r="E11" s="3">
-        <v>3.1800000000000002E-2</v>
-      </c>
-      <c r="F11" s="3">
-        <v>4.7800000000000002E-2</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0.73829999999999996</v>
-      </c>
-      <c r="H11" s="4">
-        <v>8.3699999999999997E-2</v>
-      </c>
-      <c r="I11" s="4">
-        <v>2.2599999999999999E-2</v>
-      </c>
-      <c r="J11" s="4">
-        <v>3.3599999999999998E-2</v>
-      </c>
-      <c r="K11" s="4">
-        <v>4.7899999999999998E-2</v>
-      </c>
-      <c r="L11" s="5">
-        <v>0.71079999999999999</v>
-      </c>
-      <c r="M11" s="5">
-        <v>5.96E-2</v>
-      </c>
-      <c r="N11" s="5">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="O11" s="5">
-        <v>4.8599999999999997E-2</v>
-      </c>
-      <c r="P11" s="5">
-        <v>5.3499999999999999E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="3">
-        <v>7.4709999999999999E-2</v>
-      </c>
-      <c r="C12" s="3">
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="D12" s="3">
-        <v>1.9699999999999999E-2</v>
-      </c>
-      <c r="E12" s="3">
-        <v>3.1699999999999999E-2</v>
-      </c>
-      <c r="F12" s="3">
-        <v>4.7600000000000003E-2</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0.74260000000000004</v>
-      </c>
-      <c r="H12" s="4">
-        <v>7.9899999999999999E-2</v>
-      </c>
-      <c r="I12" s="4">
-        <v>2.2100000000000002E-2</v>
-      </c>
-      <c r="J12" s="4">
-        <v>3.2099999999999997E-2</v>
-      </c>
-      <c r="K12" s="4">
-        <v>4.58E-2</v>
-      </c>
-      <c r="L12" s="8">
-        <v>0.72550000000000003</v>
-      </c>
-      <c r="M12" s="5">
-        <v>7.1300000000000002E-2</v>
-      </c>
-      <c r="N12" s="8">
-        <v>4.1799999999999997E-2</v>
-      </c>
-      <c r="O12" s="5">
-        <v>5.9900000000000002E-2</v>
-      </c>
-      <c r="P12" s="5">
-        <v>6.5000000000000002E-2</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" s="3">
-        <v>0.50019999999999998</v>
+        <v>0.66910000000000003</v>
       </c>
       <c r="C14" s="3">
-        <v>2.0500000000000001E-2</v>
+        <v>5.4199999999999998E-2</v>
       </c>
       <c r="D14" s="3">
-        <v>6.8999999999999999E-3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="E14" s="3">
-        <v>6.7000000000000002E-3</v>
+        <v>1.84E-2</v>
       </c>
       <c r="F14" s="3">
-        <v>1.01E-2</v>
+        <v>2.6700000000000002E-2</v>
       </c>
       <c r="G14" s="4">
-        <v>0.5</v>
+        <v>0.66759999999999997</v>
       </c>
       <c r="H14" s="4">
-        <v>1.6400000000000001E-2</v>
+        <v>6.1899999999999997E-2</v>
       </c>
       <c r="I14" s="4">
-        <v>8.0999999999999996E-3</v>
+        <v>1.55E-2</v>
       </c>
       <c r="J14" s="4">
-        <v>6.6E-3</v>
+        <v>2.12E-2</v>
       </c>
       <c r="K14" s="4">
-        <v>9.4000000000000004E-3</v>
+        <v>3.44E-2</v>
       </c>
       <c r="L14" s="5">
-        <v>0.504</v>
+        <v>0.67400000000000004</v>
       </c>
       <c r="M14" s="5">
-        <v>2.1100000000000001E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="N14" s="5">
-        <v>1.84E-2</v>
+        <v>3.0599999999999999E-2</v>
       </c>
       <c r="O14" s="5">
-        <v>1.7399999999999999E-2</v>
+        <v>4.9099999999999998E-2</v>
       </c>
       <c r="P14" s="5">
-        <v>1.9099999999999999E-2</v>
+        <v>5.4899999999999997E-2</v>
       </c>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="13" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B15" s="3">
-        <v>0.61499999999999999</v>
+        <v>0.68120000000000003</v>
       </c>
       <c r="C15" s="3">
-        <v>3.2199999999999999E-2</v>
+        <v>7.4899999999999994E-2</v>
       </c>
       <c r="D15" s="3">
-        <v>9.1999999999999998E-3</v>
+        <v>1.6E-2</v>
       </c>
       <c r="E15" s="3">
-        <v>8.6999999999999994E-3</v>
+        <v>2.47E-2</v>
       </c>
       <c r="F15" s="3">
-        <v>1.3599999999999999E-2</v>
+        <v>3.7100000000000001E-2</v>
       </c>
       <c r="G15" s="4">
-        <v>0.60599999999999998</v>
+        <v>0.69889999999999997</v>
       </c>
       <c r="H15" s="4">
-        <v>2.9600000000000001E-2</v>
+        <v>7.1499999999999994E-2</v>
       </c>
       <c r="I15" s="4">
-        <v>1.09E-2</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="J15" s="4">
-        <v>1.11E-2</v>
+        <v>2.86E-2</v>
       </c>
       <c r="K15" s="4">
-        <v>1.61E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="L15" s="5">
-        <v>0.62150000000000005</v>
+        <v>0.62560000000000004</v>
       </c>
       <c r="M15" s="5">
         <v>3.9399999999999998E-2</v>
       </c>
       <c r="N15" s="5">
-        <v>2.5700000000000001E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="O15" s="5">
-        <v>2.8500000000000001E-2</v>
+        <v>3.3099999999999997E-2</v>
       </c>
       <c r="P15" s="5">
-        <v>3.2800000000000003E-2</v>
+        <v>3.5900000000000001E-2</v>
       </c>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B16" s="3">
-        <v>0.67200000000000004</v>
+        <v>0.74639999999999995</v>
       </c>
       <c r="C16" s="3">
-        <v>5.3699999999999998E-2</v>
+        <v>9.7900000000000001E-2</v>
       </c>
       <c r="D16" s="3">
-        <v>1.3599999999999999E-2</v>
+        <v>1.9599999999999999E-2</v>
       </c>
       <c r="E16" s="3">
-        <v>1.77E-2</v>
+        <v>3.2300000000000002E-2</v>
       </c>
       <c r="F16" s="3">
-        <v>2.6599999999999999E-2</v>
+        <v>4.8500000000000001E-2</v>
       </c>
       <c r="G16" s="4">
-        <v>0.64049999999999996</v>
+        <v>0.73980000000000001</v>
       </c>
       <c r="H16" s="4">
-        <v>3.5999999999999997E-2</v>
+        <v>8.43E-2</v>
       </c>
       <c r="I16" s="4">
-        <v>1.35E-2</v>
+        <v>2.23E-2</v>
       </c>
       <c r="J16" s="4">
-        <v>1.44E-2</v>
+        <v>3.3799999999999997E-2</v>
       </c>
       <c r="K16" s="4">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0.71360000000000001</v>
+      </c>
+      <c r="M16" s="5">
+        <v>7.2099999999999997E-2</v>
+      </c>
+      <c r="N16" s="5">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="O16" s="5">
+        <v>6.0400000000000002E-2</v>
+      </c>
+      <c r="P16" s="5">
+        <v>6.5699999999999995E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="3">
+        <v>0.68169999999999997</v>
+      </c>
+      <c r="C17" s="3">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2.01E-2</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0.72240000000000004</v>
+      </c>
+      <c r="H17" s="4">
+        <v>7.0300000000000001E-2</v>
+      </c>
+      <c r="I17" s="4">
         <v>2.06E-2</v>
       </c>
-      <c r="L16" s="5">
-        <v>0.63139999999999996</v>
-      </c>
-      <c r="M16" s="5">
-        <v>4.9500000000000002E-2</v>
-      </c>
-      <c r="N16" s="5">
-        <v>3.1199999999999999E-2</v>
-      </c>
-      <c r="O16" s="5">
-        <v>4.1799999999999997E-2</v>
-      </c>
-      <c r="P16" s="5">
-        <v>4.53E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="3">
-        <v>0.67730000000000001</v>
-      </c>
-      <c r="C17" s="3">
-        <v>5.3400000000000003E-2</v>
-      </c>
-      <c r="D17" s="3">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1.6899999999999998E-2</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2.5600000000000001E-2</v>
-      </c>
-      <c r="G17" s="4">
-        <v>0.67310000000000003</v>
-      </c>
-      <c r="H17" s="4">
+      <c r="J17" s="4">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="K17" s="4">
+        <v>4.02E-2</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0.63149999999999995</v>
+      </c>
+      <c r="M17" s="5">
+        <v>3.6700000000000003E-2</v>
+      </c>
+      <c r="N17" s="5">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="O17" s="5">
+        <v>2.81E-2</v>
+      </c>
+      <c r="P17" s="5">
+        <v>3.15E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="6">
+        <v>0.75439999999999996</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.1104</v>
+      </c>
+      <c r="D18" s="6">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E18" s="6">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="F18" s="6">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="G18" s="7">
+        <v>0.75019999999999998</v>
+      </c>
+      <c r="H18" s="7">
+        <v>9.1600000000000001E-2</v>
+      </c>
+      <c r="I18" s="7">
+        <v>2.41E-2</v>
+      </c>
+      <c r="J18" s="7">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="K18" s="7">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="L18" s="8">
+        <v>0.7258</v>
+      </c>
+      <c r="M18" s="8">
+        <v>7.2599999999999998E-2</v>
+      </c>
+      <c r="N18" s="8">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="O18" s="8">
+        <v>6.0900000000000003E-2</v>
+      </c>
+      <c r="P18" s="8">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.74970000000000003</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.1041</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="E21" s="3">
+        <v>3.49E-2</v>
+      </c>
+      <c r="F21" s="3">
+        <v>5.2200000000000003E-2</v>
+      </c>
+      <c r="G21" s="4">
+        <v>0.74750000000000005</v>
+      </c>
+      <c r="H21" s="4">
+        <v>8.9399999999999993E-2</v>
+      </c>
+      <c r="I21" s="4">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="J21" s="4">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="K21" s="4">
         <v>5.0500000000000003E-2</v>
       </c>
-      <c r="I17" s="4">
-        <v>1.4800000000000001E-2</v>
-      </c>
-      <c r="J17" s="4">
-        <v>1.9599999999999999E-2</v>
-      </c>
-      <c r="K17" s="4">
-        <v>2.8199999999999999E-2</v>
-      </c>
-      <c r="L17" s="5">
-        <v>0.68069999999999997</v>
-      </c>
-      <c r="M17" s="5">
-        <v>5.7500000000000002E-2</v>
-      </c>
-      <c r="N17" s="5">
-        <v>3.2500000000000001E-2</v>
-      </c>
-      <c r="O17" s="5">
-        <v>4.58E-2</v>
-      </c>
-      <c r="P17" s="5">
-        <v>5.0799999999999998E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="3">
-        <v>0.67020000000000002</v>
-      </c>
-      <c r="C18" s="3">
-        <v>4.4499999999999998E-2</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1.1900000000000001E-2</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1.4200000000000001E-2</v>
-      </c>
-      <c r="F18" s="3">
-        <v>2.1499999999999998E-2</v>
-      </c>
-      <c r="G18" s="4">
-        <v>0.67569999999999997</v>
-      </c>
-      <c r="H18" s="4">
-        <v>5.1200000000000002E-2</v>
-      </c>
-      <c r="I18" s="4">
-        <v>1.5299999999999999E-2</v>
-      </c>
-      <c r="J18" s="4">
-        <v>2.0500000000000001E-2</v>
-      </c>
-      <c r="K18" s="4">
-        <v>2.92E-2</v>
-      </c>
-      <c r="L18" s="5">
-        <v>0.67300000000000004</v>
-      </c>
-      <c r="M18" s="5">
-        <v>5.96E-2</v>
-      </c>
-      <c r="N18" s="5">
-        <v>3.4200000000000001E-2</v>
-      </c>
-      <c r="O18" s="5">
-        <v>4.6899999999999997E-2</v>
-      </c>
-      <c r="P18" s="5">
-        <v>5.2400000000000002E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="3">
-        <v>0.65910000000000002</v>
-      </c>
-      <c r="C19" s="3">
-        <v>4.4200000000000003E-2</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1.2E-2</v>
-      </c>
-      <c r="E19" s="3">
-        <v>1.44E-2</v>
-      </c>
-      <c r="F19" s="3">
-        <v>2.1700000000000001E-2</v>
-      </c>
-      <c r="G19" s="4">
-        <v>0.63759999999999994</v>
-      </c>
-      <c r="H19" s="4">
-        <v>4.19E-2</v>
-      </c>
-      <c r="I19" s="4">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="J19" s="4">
-        <v>1.4500000000000001E-2</v>
-      </c>
-      <c r="K19" s="4">
-        <v>2.1399999999999999E-2</v>
-      </c>
-      <c r="L19" s="5">
-        <v>0.67400000000000004</v>
-      </c>
-      <c r="M19" s="5">
-        <v>6.25E-2</v>
-      </c>
-      <c r="N19" s="5">
-        <v>3.0599999999999999E-2</v>
-      </c>
-      <c r="O19" s="5">
-        <v>4.9099999999999998E-2</v>
-      </c>
-      <c r="P19" s="5">
-        <v>5.4899999999999997E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="3">
-        <v>0.68120000000000003</v>
-      </c>
-      <c r="C20" s="3">
-        <v>7.4899999999999994E-2</v>
-      </c>
-      <c r="D20" s="3">
-        <v>1.6E-2</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2.47E-2</v>
-      </c>
-      <c r="F20" s="3">
-        <v>3.7100000000000001E-2</v>
-      </c>
-      <c r="G20" s="4">
-        <v>0.69889999999999997</v>
-      </c>
-      <c r="H20" s="4">
-        <v>7.1499999999999994E-2</v>
-      </c>
-      <c r="I20" s="4">
-        <v>1.9800000000000002E-2</v>
-      </c>
-      <c r="J20" s="4">
-        <v>2.86E-2</v>
-      </c>
-      <c r="K20" s="4">
-        <v>4.0800000000000003E-2</v>
-      </c>
-      <c r="L20" s="5">
-        <v>0.62560000000000004</v>
-      </c>
-      <c r="M20" s="5">
-        <v>3.9399999999999998E-2</v>
-      </c>
-      <c r="N20" s="5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="O20" s="5">
-        <v>3.3099999999999997E-2</v>
-      </c>
-      <c r="P20" s="5">
-        <v>3.5900000000000001E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="3">
-        <v>0.74639999999999995</v>
-      </c>
-      <c r="C21" s="3">
-        <v>9.7900000000000001E-2</v>
-      </c>
-      <c r="D21" s="3">
-        <v>1.9599999999999999E-2</v>
-      </c>
-      <c r="E21" s="3">
-        <v>3.2300000000000002E-2</v>
-      </c>
-      <c r="F21" s="3">
-        <v>4.8500000000000001E-2</v>
-      </c>
-      <c r="G21" s="4">
-        <v>0.73980000000000001</v>
-      </c>
-      <c r="H21" s="4">
-        <v>8.43E-2</v>
-      </c>
-      <c r="I21" s="4">
-        <v>2.23E-2</v>
-      </c>
-      <c r="J21" s="4">
-        <v>3.3799999999999997E-2</v>
-      </c>
-      <c r="K21" s="4">
-        <v>4.8300000000000003E-2</v>
-      </c>
       <c r="L21" s="5">
-        <v>0.71360000000000001</v>
+        <v>0.72060000000000002</v>
       </c>
       <c r="M21" s="5">
-        <v>7.2099999999999997E-2</v>
+        <v>7.0199999999999999E-2</v>
       </c>
       <c r="N21" s="5">
         <v>3.9699999999999999E-2</v>
       </c>
-      <c r="O21" s="8">
-        <v>6.0400000000000002E-2</v>
-      </c>
-      <c r="P21" s="8">
-        <v>6.5699999999999995E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="13" t="s">
+      <c r="O21" s="5">
+        <v>5.74E-2</v>
+      </c>
+      <c r="P21" s="5">
+        <v>6.3299999999999995E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0.74770000000000003</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.10340000000000001</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1.9900000000000001E-2</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3.4099999999999998E-2</v>
+      </c>
+      <c r="F22" s="3">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="G22" s="4">
+        <v>0.74209999999999998</v>
+      </c>
+      <c r="H22" s="4">
+        <v>0.09</v>
+      </c>
+      <c r="I22" s="4">
+        <v>2.29E-2</v>
+      </c>
+      <c r="J22" s="4">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="K22" s="4">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="L22" s="5">
+        <v>0.71550000000000002</v>
+      </c>
+      <c r="M22" s="5">
+        <v>6.9099999999999995E-2</v>
+      </c>
+      <c r="N22" s="5">
+        <v>3.9100000000000003E-2</v>
+      </c>
+      <c r="O22" s="5">
+        <v>5.6800000000000003E-2</v>
+      </c>
+      <c r="P22" s="5">
+        <v>6.1899999999999997E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.74580000000000002</v>
+      </c>
+      <c r="C23" s="3">
+        <v>9.6299999999999997E-2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="E23" s="3">
+        <v>3.1800000000000002E-2</v>
+      </c>
+      <c r="F23" s="3">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="G23" s="4">
+        <v>0.73829999999999996</v>
+      </c>
+      <c r="H23" s="4">
+        <v>8.3699999999999997E-2</v>
+      </c>
+      <c r="I23" s="4">
+        <v>2.2599999999999999E-2</v>
+      </c>
+      <c r="J23" s="4">
+        <v>3.3599999999999998E-2</v>
+      </c>
+      <c r="K23" s="4">
+        <v>4.7899999999999998E-2</v>
+      </c>
+      <c r="L23" s="5">
+        <v>0.71079999999999999</v>
+      </c>
+      <c r="M23" s="5">
+        <v>5.96E-2</v>
+      </c>
+      <c r="N23" s="5">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="O23" s="5">
+        <v>4.8599999999999997E-2</v>
+      </c>
+      <c r="P23" s="5">
+        <v>5.3499999999999999E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="C24" s="3">
+        <v>9.2399999999999996E-2</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1.78E-2</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3.0499999999999999E-2</v>
+      </c>
+      <c r="F24" s="3">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="G24" s="4">
+        <v>0.73560000000000003</v>
+      </c>
+      <c r="H24" s="4">
+        <v>7.9899999999999999E-2</v>
+      </c>
+      <c r="I24" s="4">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J24" s="4">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="K24" s="4">
+        <v>4.48E-2</v>
+      </c>
+      <c r="L24" s="5">
+        <v>0.72130000000000005</v>
+      </c>
+      <c r="M24" s="5">
+        <v>6.9800000000000001E-2</v>
+      </c>
+      <c r="N24" s="5">
+        <v>3.85E-2</v>
+      </c>
+      <c r="O24" s="5">
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="P24" s="5">
+        <v>6.2700000000000006E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0.74839999999999995</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.1023</v>
+      </c>
+      <c r="D25" s="3">
+        <v>2.06E-2</v>
+      </c>
+      <c r="E25" s="3">
+        <v>3.3700000000000001E-2</v>
+      </c>
+      <c r="F25" s="3">
+        <v>5.0599999999999999E-2</v>
+      </c>
+      <c r="G25" s="4">
+        <v>0.74690000000000001</v>
+      </c>
+      <c r="H25" s="4">
+        <v>8.7599999999999997E-2</v>
+      </c>
+      <c r="I25" s="4">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="J25" s="4">
+        <v>3.2199999999999999E-2</v>
+      </c>
+      <c r="K25" s="4">
+        <v>4.6699999999999998E-2</v>
+      </c>
+      <c r="L25" s="5">
+        <v>0.7218</v>
+      </c>
+      <c r="M25" s="5">
+        <v>7.0300000000000001E-2</v>
+      </c>
+      <c r="N25" s="5">
+        <v>4.0099999999999997E-2</v>
+      </c>
+      <c r="O25" s="5">
+        <v>5.8900000000000001E-2</v>
+      </c>
+      <c r="P25" s="5">
+        <v>6.3600000000000004E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="3">
-        <v>0.68169999999999997</v>
-      </c>
-      <c r="C22" s="3">
-        <v>6.0999999999999999E-2</v>
-      </c>
-      <c r="D22" s="3">
-        <v>1.5599999999999999E-2</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2.01E-2</v>
-      </c>
-      <c r="F22" s="3">
-        <v>3.0200000000000001E-2</v>
-      </c>
-      <c r="G22" s="4">
-        <v>0.72240000000000004</v>
-      </c>
-      <c r="H22" s="4">
-        <v>7.0300000000000001E-2</v>
-      </c>
-      <c r="I22" s="4">
+      <c r="B26" s="6">
+        <v>0.75439999999999996</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.1104</v>
+      </c>
+      <c r="D26" s="6">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E26" s="6">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="F26" s="6">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="G26" s="7">
+        <v>0.75019999999999998</v>
+      </c>
+      <c r="H26" s="7">
+        <v>9.1600000000000001E-2</v>
+      </c>
+      <c r="I26" s="7">
+        <v>2.41E-2</v>
+      </c>
+      <c r="J26" s="7">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="K26" s="7">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="L26" s="8">
+        <v>0.7258</v>
+      </c>
+      <c r="M26" s="8">
+        <v>7.2599999999999998E-2</v>
+      </c>
+      <c r="N26" s="8">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="O26" s="8">
+        <v>6.0900000000000003E-2</v>
+      </c>
+      <c r="P26" s="8">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="3">
+        <v>0.75180000000000002</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.1089</v>
+      </c>
+      <c r="D29" s="3">
         <v>2.06E-2</v>
       </c>
-      <c r="J22" s="4">
-        <v>2.8199999999999999E-2</v>
-      </c>
-      <c r="K22" s="4">
-        <v>4.02E-2</v>
-      </c>
-      <c r="L22" s="5">
-        <v>0.63149999999999995</v>
-      </c>
-      <c r="M22" s="5">
+      <c r="E29" s="3">
+        <v>3.5499999999999997E-2</v>
+      </c>
+      <c r="F29" s="3">
+        <v>5.3699999999999998E-2</v>
+      </c>
+      <c r="G29" s="4">
+        <v>0.749</v>
+      </c>
+      <c r="H29" s="4">
+        <v>8.9599999999999999E-2</v>
+      </c>
+      <c r="I29" s="4">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="J29" s="4">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="K29" s="4">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="L29" s="5">
+        <v>0.72529999999999994</v>
+      </c>
+      <c r="M29" s="5">
+        <v>7.2700000000000001E-2</v>
+      </c>
+      <c r="N29" s="5">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="O29" s="5">
+        <v>6.0900000000000003E-2</v>
+      </c>
+      <c r="P29" s="5">
+        <v>6.6199999999999995E-2</v>
+      </c>
+      <c r="R29" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="6">
+        <v>0.75439999999999996</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.1104</v>
+      </c>
+      <c r="D30" s="6">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E30" s="6">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="F30" s="6">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="G30" s="7">
+        <v>0.75019999999999998</v>
+      </c>
+      <c r="H30" s="7">
+        <v>9.1600000000000001E-2</v>
+      </c>
+      <c r="I30" s="7">
+        <v>2.41E-2</v>
+      </c>
+      <c r="J30" s="7">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="K30" s="7">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="L30" s="8">
+        <v>0.7258</v>
+      </c>
+      <c r="M30" s="8">
+        <v>7.2599999999999998E-2</v>
+      </c>
+      <c r="N30" s="8">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="O30" s="8">
+        <v>6.0900000000000003E-2</v>
+      </c>
+      <c r="P30" s="8">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="R30" s="9"/>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" s="3">
+        <v>0.754</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0.10829999999999999</v>
+      </c>
+      <c r="D31" s="3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E31" s="3">
+        <v>3.6200000000000003E-2</v>
+      </c>
+      <c r="F31" s="3">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="G31" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="H31" s="4">
+        <v>9.0300000000000005E-2</v>
+      </c>
+      <c r="I31" s="4">
+        <v>2.3900000000000001E-2</v>
+      </c>
+      <c r="J31" s="4">
+        <v>3.61E-2</v>
+      </c>
+      <c r="K31" s="4">
+        <v>5.2200000000000003E-2</v>
+      </c>
+      <c r="L31" s="5">
+        <v>0.72670000000000001</v>
+      </c>
+      <c r="M31" s="5">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="N31" s="5">
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="O31" s="5">
+        <v>5.8900000000000001E-2</v>
+      </c>
+      <c r="P31" s="5">
+        <v>6.4500000000000002E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="3">
+        <v>0.75260000000000005</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.1053</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E32" s="3">
+        <v>3.4500000000000003E-2</v>
+      </c>
+      <c r="F32" s="3">
+        <v>5.1999999999999998E-2</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0.74929999999999997</v>
+      </c>
+      <c r="H32" s="4">
+        <v>8.9099999999999999E-2</v>
+      </c>
+      <c r="I32" s="4">
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="J32" s="4">
+        <v>3.5799999999999998E-2</v>
+      </c>
+      <c r="K32" s="4">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="L32" s="5">
+        <v>0.72150000000000003</v>
+      </c>
+      <c r="M32" s="5">
+        <v>6.6400000000000001E-2</v>
+      </c>
+      <c r="N32" s="5">
+        <v>4.0300000000000002E-2</v>
+      </c>
+      <c r="O32" s="5">
+        <v>5.6899999999999999E-2</v>
+      </c>
+      <c r="P32" s="5">
+        <v>6.2199999999999998E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="3">
+        <v>0.75280000000000002</v>
+      </c>
+      <c r="C34" s="3">
+        <v>0.1061</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2.06E-2</v>
+      </c>
+      <c r="E34" s="3">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="F34" s="3">
+        <v>5.3100000000000001E-2</v>
+      </c>
+      <c r="G34" s="4">
+        <v>0.74950000000000006</v>
+      </c>
+      <c r="H34" s="4">
+        <v>9.06E-2</v>
+      </c>
+      <c r="I34" s="4">
+        <v>2.4E-2</v>
+      </c>
+      <c r="J34" s="4">
+        <v>3.6400000000000002E-2</v>
+      </c>
+      <c r="K34" s="4">
+        <v>5.1900000000000002E-2</v>
+      </c>
+      <c r="L34" s="5">
+        <v>0.72399999999999998</v>
+      </c>
+      <c r="M34" s="5">
+        <v>7.0099999999999996E-2</v>
+      </c>
+      <c r="N34" s="5">
+        <v>4.2200000000000001E-2</v>
+      </c>
+      <c r="O34" s="5">
+        <v>5.8299999999999998E-2</v>
+      </c>
+      <c r="P34" s="5">
+        <v>6.3100000000000003E-2</v>
+      </c>
+      <c r="R34" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
+      <c r="A35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="6">
+        <v>0.75439999999999996</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.1104</v>
+      </c>
+      <c r="D35" s="6">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E35" s="6">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="F35" s="6">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="G35" s="7">
+        <v>0.75019999999999998</v>
+      </c>
+      <c r="H35" s="7">
+        <v>9.1600000000000001E-2</v>
+      </c>
+      <c r="I35" s="7">
+        <v>2.41E-2</v>
+      </c>
+      <c r="J35" s="7">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="K35" s="7">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="L35" s="8">
+        <v>0.7258</v>
+      </c>
+      <c r="M35" s="8">
+        <v>7.2599999999999998E-2</v>
+      </c>
+      <c r="N35" s="8">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="O35" s="8">
+        <v>6.0900000000000003E-2</v>
+      </c>
+      <c r="P35" s="8">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="3">
+        <v>0.75409999999999999</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0.1099</v>
+      </c>
+      <c r="D36" s="3">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="E36" s="3">
+        <v>3.61E-2</v>
+      </c>
+      <c r="F36" s="3">
+        <v>5.4199999999999998E-2</v>
+      </c>
+      <c r="G36" s="4">
+        <v>0.74990000000000001</v>
+      </c>
+      <c r="H36" s="4">
+        <v>9.2700000000000005E-2</v>
+      </c>
+      <c r="I36" s="4">
+        <v>2.4E-2</v>
+      </c>
+      <c r="J36" s="4">
+        <v>3.7199999999999997E-2</v>
+      </c>
+      <c r="K36" s="4">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="L36" s="5">
+        <v>0.72519999999999996</v>
+      </c>
+      <c r="M36" s="5">
+        <v>7.2499999999999995E-2</v>
+      </c>
+      <c r="N36" s="5">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="O36" s="5">
+        <v>6.0699999999999997E-2</v>
+      </c>
+      <c r="P36" s="5">
+        <v>6.5199999999999994E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
+      <c r="A37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="3">
+        <v>0.75449999999999995</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0.1106</v>
+      </c>
+      <c r="D37" s="3">
+        <v>2.1299999999999999E-2</v>
+      </c>
+      <c r="E37" s="3">
         <v>3.6700000000000003E-2</v>
       </c>
-      <c r="N22" s="5">
-        <v>2.7900000000000001E-2</v>
-      </c>
-      <c r="O22" s="5">
-        <v>2.81E-2</v>
-      </c>
-      <c r="P22" s="5">
-        <v>3.15E-2</v>
+      <c r="F37" s="3">
+        <v>5.5E-2</v>
+      </c>
+      <c r="G37" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="H37" s="4">
+        <v>9.2899999999999996E-2</v>
+      </c>
+      <c r="I37" s="4">
+        <v>2.3800000000000002E-2</v>
+      </c>
+      <c r="J37" s="4">
+        <v>3.73E-2</v>
+      </c>
+      <c r="K37" s="4">
+        <v>5.3199999999999997E-2</v>
+      </c>
+      <c r="L37" s="5">
+        <v>0.72589999999999999</v>
+      </c>
+      <c r="M37" s="5">
+        <v>7.2900000000000006E-2</v>
+      </c>
+      <c r="N37" s="5">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="O37" s="5">
+        <v>6.0900000000000003E-2</v>
+      </c>
+      <c r="P37" s="5">
+        <v>6.5799999999999997E-2</v>
       </c>
     </row>
   </sheetData>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,32 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92160082-7FA1-AF4E-899D-36FDD1B3F7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F30338E-A850-EA45-A236-EDE98318C1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="54900" yWindow="-6020" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="59">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,10 +78,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Full_noOth</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>reg=0.01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -84,22 +90,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>no focr</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>no nei</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>no mr1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>no mr2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Soc1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -108,10 +98,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Com1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>朋友友谊关系；商家链接关系</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -141,10 +127,6 @@
   </si>
   <si>
     <t>CMR_GNN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Full_ClaOthBest</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -337,10 +319,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>MoGEAD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>MMoE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -350,6 +328,66 @@
   </si>
   <si>
     <t>GEOM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Busi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Edges</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Nodes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Delay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MoEAD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AUC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Prec@2%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Metric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w/o Orth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w/o CE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w/o RANE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w/o DMNE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w/o IMNE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -360,7 +398,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -401,8 +439,22 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -436,6 +488,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,10 +579,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -540,6 +599,11 @@
     <xf numFmtId="176" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -564,14 +628,27 @@
     <xf numFmtId="176" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -865,27 +942,27 @@
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="22"/>
+      <c r="B1" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
       <c r="R1" s="2" t="s">
         <v>2</v>
       </c>
@@ -944,142 +1021,142 @@
       </c>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="23"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="26"/>
+      <c r="A3" s="15"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="18"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="16">
+        <v>0.75170000000000003</v>
+      </c>
+      <c r="C4" s="16">
+        <v>2.06E-2</v>
+      </c>
+      <c r="D4" s="16">
+        <v>3.4599999999999999E-2</v>
+      </c>
+      <c r="E4" s="16">
+        <v>5.21E-2</v>
+      </c>
+      <c r="F4" s="16">
+        <v>0.1055</v>
+      </c>
+      <c r="G4" s="17">
+        <v>0.749</v>
+      </c>
+      <c r="H4" s="17">
+        <v>2.3599999999999999E-2</v>
+      </c>
+      <c r="I4" s="17">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="J4" s="17">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="K4" s="17">
+        <v>8.9399999999999993E-2</v>
+      </c>
+      <c r="L4" s="18">
+        <v>0.72509999999999997</v>
+      </c>
+      <c r="M4" s="18">
+        <v>4.07E-2</v>
+      </c>
+      <c r="N4" s="18">
+        <v>5.9799999999999999E-2</v>
+      </c>
+      <c r="O4" s="19">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P4" s="18">
+        <v>7.1199999999999999E-2</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
+      <c r="A5" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="16">
+        <v>0.75249999999999995</v>
+      </c>
+      <c r="C5" s="16">
+        <v>2.07E-2</v>
+      </c>
+      <c r="D5" s="16">
+        <v>3.5099999999999999E-2</v>
+      </c>
+      <c r="E5" s="16">
+        <v>5.28E-2</v>
+      </c>
+      <c r="F5" s="16">
+        <v>0.1069</v>
+      </c>
+      <c r="G5" s="17">
+        <v>0.74860000000000004</v>
+      </c>
+      <c r="H5" s="17">
+        <v>2.3900000000000001E-2</v>
+      </c>
+      <c r="I5" s="17">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="J5" s="17">
+        <v>5.1400000000000001E-2</v>
+      </c>
+      <c r="K5" s="17">
+        <v>8.9700000000000002E-2</v>
+      </c>
+      <c r="L5" s="18">
+        <v>0.72509999999999997</v>
+      </c>
+      <c r="M5" s="18">
+        <v>4.0599999999999997E-2</v>
+      </c>
+      <c r="N5" s="18">
+        <v>5.62E-2</v>
+      </c>
+      <c r="O5" s="19">
+        <v>6.1199999999999997E-2</v>
+      </c>
+      <c r="P5" s="18">
+        <v>6.7299999999999999E-2</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" s="24">
-        <v>0.75170000000000003</v>
-      </c>
-      <c r="C4" s="24">
-        <v>2.06E-2</v>
-      </c>
-      <c r="D4" s="24">
-        <v>3.4599999999999999E-2</v>
-      </c>
-      <c r="E4" s="24">
-        <v>5.21E-2</v>
-      </c>
-      <c r="F4" s="24">
-        <v>0.1055</v>
-      </c>
-      <c r="G4" s="25">
-        <v>0.749</v>
-      </c>
-      <c r="H4" s="25">
-        <v>2.3599999999999999E-2</v>
-      </c>
-      <c r="I4" s="25">
-        <v>3.5900000000000001E-2</v>
-      </c>
-      <c r="J4" s="25">
-        <v>5.1200000000000002E-2</v>
-      </c>
-      <c r="K4" s="25">
-        <v>8.9399999999999993E-2</v>
-      </c>
-      <c r="L4" s="26">
-        <v>0.72509999999999997</v>
-      </c>
-      <c r="M4" s="26">
-        <v>4.07E-2</v>
-      </c>
-      <c r="N4" s="26">
-        <v>5.9799999999999999E-2</v>
-      </c>
-      <c r="O4" s="27">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="P4" s="26">
-        <v>7.1199999999999999E-2</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="24">
-        <v>0.75249999999999995</v>
-      </c>
-      <c r="C5" s="24">
-        <v>2.07E-2</v>
-      </c>
-      <c r="D5" s="24">
-        <v>3.5099999999999999E-2</v>
-      </c>
-      <c r="E5" s="24">
-        <v>5.28E-2</v>
-      </c>
-      <c r="F5" s="24">
-        <v>0.1069</v>
-      </c>
-      <c r="G5" s="25">
-        <v>0.74860000000000004</v>
-      </c>
-      <c r="H5" s="25">
-        <v>2.3900000000000001E-2</v>
-      </c>
-      <c r="I5" s="25">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="J5" s="25">
-        <v>5.1400000000000001E-2</v>
-      </c>
-      <c r="K5" s="25">
-        <v>8.9700000000000002E-2</v>
-      </c>
-      <c r="L5" s="26">
-        <v>0.72509999999999997</v>
-      </c>
-      <c r="M5" s="26">
-        <v>4.0599999999999997E-2</v>
-      </c>
-      <c r="N5" s="26">
-        <v>5.62E-2</v>
-      </c>
-      <c r="O5" s="27">
-        <v>6.1199999999999997E-2</v>
-      </c>
-      <c r="P5" s="26">
-        <v>6.7299999999999999E-2</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:18">
       <c r="R6" s="9" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="11" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="B8" s="3">
         <v>0.75180000000000002</v>
@@ -1127,12 +1204,12 @@
         <v>7.2700000000000001E-2</v>
       </c>
       <c r="R8" s="14" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B9" s="6">
         <v>0.75439999999999996</v>
@@ -1183,7 +1260,7 @@
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B10" s="3">
         <v>0.754</v>
@@ -1233,7 +1310,7 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B11" s="3">
         <v>0.75260000000000005</v>
@@ -1283,7 +1360,7 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B13" s="3">
         <v>0.75280000000000002</v>
@@ -1331,12 +1408,12 @@
         <v>7.0099999999999996E-2</v>
       </c>
       <c r="R13" s="14" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B14" s="6">
         <v>0.75439999999999996</v>
@@ -1386,7 +1463,7 @@
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B15" s="3">
         <v>0.75409999999999999</v>
@@ -1436,7 +1513,7 @@
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3">
         <v>0.75449999999999995</v>
@@ -1486,7 +1563,7 @@
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="10" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
         <v>0.50019999999999998</v>
@@ -1527,7 +1604,7 @@
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="10" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B20" s="3">
         <v>0.61499999999999999</v>
@@ -1568,7 +1645,7 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B21" s="3">
         <v>0.67200000000000004</v>
@@ -1609,7 +1686,7 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B22" s="3">
         <v>0.67730000000000001</v>
@@ -1650,7 +1727,7 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="10" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B23" s="3">
         <v>0.67020000000000002</v>
@@ -1691,7 +1768,7 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="10" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B24" s="3">
         <v>0.66910000000000003</v>
@@ -1732,7 +1809,7 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B25" s="3">
         <v>0.68120000000000003</v>
@@ -1771,12 +1848,12 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="10" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B26" s="3">
         <v>0.74639999999999995</v>
@@ -1815,12 +1892,12 @@
         <v>6.5699999999999995E-2</v>
       </c>
       <c r="R26" s="9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:18">
       <c r="A27" s="10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B27" s="3">
         <v>0.68169999999999997</v>
@@ -1861,7 +1938,7 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B28" s="6">
         <v>0.75439999999999996</v>
@@ -1900,17 +1977,67 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
+    <row r="29" spans="1:18">
+      <c r="B29" s="3">
+        <f>(B28-B26)/B26</f>
+        <v>1.0718113612004298E-2</v>
+      </c>
+      <c r="C29" s="3">
+        <f t="shared" ref="C29:E29" si="0">(C28-C26)/C26</f>
+        <v>7.1428571428571536E-2</v>
+      </c>
+      <c r="D29" s="3">
+        <f t="shared" si="0"/>
+        <v>0.13312693498452005</v>
+      </c>
+      <c r="E29" s="3">
+        <f t="shared" si="0"/>
+        <v>0.13195876288659786</v>
+      </c>
+      <c r="G29" s="4">
+        <f>(G28-G26)/G26</f>
+        <v>1.405785347391182E-2</v>
+      </c>
+      <c r="H29" s="4">
+        <f t="shared" ref="H29" si="1">(H28-H26)/H26</f>
+        <v>8.0717488789237651E-2</v>
+      </c>
+      <c r="I29" s="4">
+        <f t="shared" ref="I29" si="2">(I28-I26)/I26</f>
+        <v>9.1715976331361124E-2</v>
+      </c>
+      <c r="J29" s="4">
+        <f t="shared" ref="J29" si="3">(J28-J26)/J26</f>
+        <v>8.9026915113871591E-2</v>
+      </c>
+      <c r="L29" s="5">
+        <f>(L28-L26)/L26</f>
+        <v>1.7096412556053795E-2</v>
+      </c>
+      <c r="M29" s="5">
+        <f t="shared" ref="M29" si="4">(M28-M26)/M26</f>
+        <v>3.7783375314861492E-2</v>
+      </c>
+      <c r="N29" s="5">
+        <f t="shared" ref="N29" si="5">(N28-N26)/N26</f>
+        <v>8.278145695364246E-3</v>
+      </c>
+      <c r="O29" s="12">
+        <f t="shared" ref="O29" si="6">(O28-O26)/O26</f>
+        <v>4.566210045662232E-3</v>
+      </c>
+    </row>
     <row r="30" spans="1:18">
       <c r="A30" s="11" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:18">
       <c r="A31" s="1" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="B31" s="3">
         <v>0.74970000000000003</v>
@@ -1951,7 +2078,7 @@
     </row>
     <row r="32" spans="1:18">
       <c r="A32" s="1" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="B32" s="3">
         <v>0.74770000000000003</v>
@@ -1992,7 +2119,7 @@
     </row>
     <row r="33" spans="1:18">
       <c r="A33" s="1" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="B33" s="3">
         <v>0.74580000000000002</v>
@@ -2033,7 +2160,7 @@
     </row>
     <row r="34" spans="1:18">
       <c r="A34" s="1" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="B34" s="3">
         <v>0.73699999999999999</v>
@@ -2074,7 +2201,7 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="1" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="B35" s="3">
         <v>0.74839999999999995</v>
@@ -2115,7 +2242,7 @@
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B36" s="6">
         <v>0.75439999999999996</v>
@@ -2156,45 +2283,45 @@
     </row>
     <row r="38" spans="1:18">
       <c r="B38" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="M38" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="N38" s="5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="O38" s="12" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:18">
       <c r="A39" s="10" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B39" s="3">
         <v>9.4999999999999998E-3</v>
@@ -2233,12 +2360,12 @@
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="R39" s="14" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:18">
       <c r="A40" s="10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B40" s="3">
         <v>2.01E-2</v>
@@ -2279,7 +2406,7 @@
     </row>
     <row r="41" spans="1:18">
       <c r="A41" s="10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B41" s="3">
         <v>2.6800000000000001E-2</v>
@@ -2320,7 +2447,7 @@
     </row>
     <row r="42" spans="1:18">
       <c r="A42" s="10" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B42" s="3">
         <v>2.18E-2</v>
@@ -2361,7 +2488,7 @@
     </row>
     <row r="43" spans="1:18">
       <c r="A43" s="10" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B43" s="3">
         <v>2.5399999999999999E-2</v>
@@ -2402,7 +2529,7 @@
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B44" s="3">
         <v>3.6200000000000003E-2</v>
@@ -2443,7 +2570,7 @@
     </row>
     <row r="45" spans="1:18">
       <c r="A45" s="10" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B45" s="3">
         <v>4.0399999999999998E-2</v>
@@ -2484,7 +2611,7 @@
     </row>
     <row r="46" spans="1:18">
       <c r="A46" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B46" s="3">
         <v>5.0700000000000002E-2</v>
@@ -2536,10 +2663,607 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21DE89CC-DA89-E849-8426-98934B0A771A}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="29">
+        <v>287195</v>
+      </c>
+      <c r="C2" s="29">
+        <v>410223</v>
+      </c>
+      <c r="D2" s="29">
+        <v>48843</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="29">
+        <v>408239</v>
+      </c>
+      <c r="C3" s="29">
+        <v>568694</v>
+      </c>
+      <c r="D3" s="29">
+        <v>85590</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="29">
+        <v>405543</v>
+      </c>
+      <c r="C4" s="29">
+        <v>564129</v>
+      </c>
+      <c r="D4" s="29">
+        <v>84136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="29">
+        <v>2696</v>
+      </c>
+      <c r="C5" s="29">
+        <v>4565</v>
+      </c>
+      <c r="D5" s="29">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="30"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+    </row>
+    <row r="17" spans="1:13" s="28" customFormat="1" ht="14">
+      <c r="A17" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+    </row>
+    <row r="18" spans="1:13" ht="16">
+      <c r="A18" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="J18" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="K18" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="M18" s="34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="16">
+      <c r="A19" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="34">
+        <v>0.50019999999999998</v>
+      </c>
+      <c r="C19" s="34">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="D19" s="34">
+        <v>6.7000000000000002E-3</v>
+      </c>
+      <c r="E19" s="34">
+        <v>1.01E-2</v>
+      </c>
+      <c r="F19" s="34">
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="34">
+        <v>8.0999999999999996E-3</v>
+      </c>
+      <c r="H19" s="34">
+        <v>6.6E-3</v>
+      </c>
+      <c r="I19" s="34">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="J19" s="34">
+        <v>0.504</v>
+      </c>
+      <c r="K19" s="34">
+        <v>1.84E-2</v>
+      </c>
+      <c r="L19" s="34">
+        <v>1.7399999999999999E-2</v>
+      </c>
+      <c r="M19" s="34">
+        <v>1.9099999999999999E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="16">
+      <c r="A20" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="34">
+        <v>0.61499999999999999</v>
+      </c>
+      <c r="C20" s="34">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="D20" s="34">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="E20" s="34">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="F20" s="34">
+        <v>0.60599999999999998</v>
+      </c>
+      <c r="G20" s="34">
+        <v>1.09E-2</v>
+      </c>
+      <c r="H20" s="34">
+        <v>1.11E-2</v>
+      </c>
+      <c r="I20" s="34">
+        <v>1.61E-2</v>
+      </c>
+      <c r="J20" s="34">
+        <v>0.62150000000000005</v>
+      </c>
+      <c r="K20" s="34">
+        <v>2.5700000000000001E-2</v>
+      </c>
+      <c r="L20" s="34">
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="M20" s="34">
+        <v>3.2800000000000003E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="16">
+      <c r="A21" s="31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="34">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="C21" s="34">
+        <v>1.3599999999999999E-2</v>
+      </c>
+      <c r="D21" s="34">
+        <v>1.77E-2</v>
+      </c>
+      <c r="E21" s="34">
+        <v>2.6599999999999999E-2</v>
+      </c>
+      <c r="F21" s="34">
+        <v>0.64049999999999996</v>
+      </c>
+      <c r="G21" s="34">
+        <v>1.35E-2</v>
+      </c>
+      <c r="H21" s="34">
+        <v>1.44E-2</v>
+      </c>
+      <c r="I21" s="34">
+        <v>2.06E-2</v>
+      </c>
+      <c r="J21" s="34">
+        <v>0.63139999999999996</v>
+      </c>
+      <c r="K21" s="34">
+        <v>3.1199999999999999E-2</v>
+      </c>
+      <c r="L21" s="34">
+        <v>4.1799999999999997E-2</v>
+      </c>
+      <c r="M21" s="34">
+        <v>4.53E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="16">
+      <c r="A22" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="34">
+        <v>0.67730000000000001</v>
+      </c>
+      <c r="C22" s="34">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="D22" s="34">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="E22" s="34">
+        <v>2.5600000000000001E-2</v>
+      </c>
+      <c r="F22" s="34">
+        <v>0.67310000000000003</v>
+      </c>
+      <c r="G22" s="34">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="H22" s="34">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="I22" s="34">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="J22" s="34">
+        <v>0.68069999999999997</v>
+      </c>
+      <c r="K22" s="34">
+        <v>3.2500000000000001E-2</v>
+      </c>
+      <c r="L22" s="34">
+        <v>4.58E-2</v>
+      </c>
+      <c r="M22" s="34">
+        <v>5.0799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="16">
+      <c r="A23" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="34">
+        <v>0.67020000000000002</v>
+      </c>
+      <c r="C23" s="34">
+        <v>1.1900000000000001E-2</v>
+      </c>
+      <c r="D23" s="34">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="E23" s="34">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="F23" s="34">
+        <v>0.67569999999999997</v>
+      </c>
+      <c r="G23" s="34">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="H23" s="34">
+        <v>2.0500000000000001E-2</v>
+      </c>
+      <c r="I23" s="34">
+        <v>2.92E-2</v>
+      </c>
+      <c r="J23" s="34">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="K23" s="34">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="L23" s="34">
+        <v>4.6899999999999997E-2</v>
+      </c>
+      <c r="M23" s="34">
+        <v>5.2400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="16">
+      <c r="A24" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="34">
+        <v>0.66910000000000003</v>
+      </c>
+      <c r="C24" s="34">
+        <v>1.4E-2</v>
+      </c>
+      <c r="D24" s="34">
+        <v>1.84E-2</v>
+      </c>
+      <c r="E24" s="34">
+        <v>2.6700000000000002E-2</v>
+      </c>
+      <c r="F24" s="34">
+        <v>0.66759999999999997</v>
+      </c>
+      <c r="G24" s="34">
+        <v>1.55E-2</v>
+      </c>
+      <c r="H24" s="34">
+        <v>2.12E-2</v>
+      </c>
+      <c r="I24" s="34">
+        <v>3.44E-2</v>
+      </c>
+      <c r="J24" s="34">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="K24" s="34">
+        <v>3.0599999999999999E-2</v>
+      </c>
+      <c r="L24" s="34">
+        <v>4.9099999999999998E-2</v>
+      </c>
+      <c r="M24" s="34">
+        <v>5.4899999999999997E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="16">
+      <c r="A25" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="34">
+        <v>0.68120000000000003</v>
+      </c>
+      <c r="C25" s="34">
+        <v>1.6E-2</v>
+      </c>
+      <c r="D25" s="34">
+        <v>2.47E-2</v>
+      </c>
+      <c r="E25" s="34">
+        <v>3.7100000000000001E-2</v>
+      </c>
+      <c r="F25" s="34">
+        <v>0.69889999999999997</v>
+      </c>
+      <c r="G25" s="34">
+        <v>1.9800000000000002E-2</v>
+      </c>
+      <c r="H25" s="34">
+        <v>2.86E-2</v>
+      </c>
+      <c r="I25" s="34">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="J25" s="34">
+        <v>0.62560000000000004</v>
+      </c>
+      <c r="K25" s="34">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="L25" s="34">
+        <v>3.3099999999999997E-2</v>
+      </c>
+      <c r="M25" s="34">
+        <v>3.5900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="16">
+      <c r="A26" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="34">
+        <v>0.74639999999999995</v>
+      </c>
+      <c r="C26" s="34">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="D26" s="34">
+        <v>3.2300000000000002E-2</v>
+      </c>
+      <c r="E26" s="34">
+        <v>4.8500000000000001E-2</v>
+      </c>
+      <c r="F26" s="34">
+        <v>0.73980000000000001</v>
+      </c>
+      <c r="G26" s="34">
+        <v>2.23E-2</v>
+      </c>
+      <c r="H26" s="34">
+        <v>3.3799999999999997E-2</v>
+      </c>
+      <c r="I26" s="34">
+        <v>4.8300000000000003E-2</v>
+      </c>
+      <c r="J26" s="34">
+        <v>0.71360000000000001</v>
+      </c>
+      <c r="K26" s="34">
+        <v>3.9699999999999999E-2</v>
+      </c>
+      <c r="L26" s="34">
+        <v>6.0400000000000002E-2</v>
+      </c>
+      <c r="M26" s="34">
+        <v>6.5699999999999995E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="16">
+      <c r="A27" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="34">
+        <v>0.68169999999999997</v>
+      </c>
+      <c r="C27" s="34">
+        <v>1.5599999999999999E-2</v>
+      </c>
+      <c r="D27" s="34">
+        <v>2.01E-2</v>
+      </c>
+      <c r="E27" s="34">
+        <v>3.0200000000000001E-2</v>
+      </c>
+      <c r="F27" s="34">
+        <v>0.72240000000000004</v>
+      </c>
+      <c r="G27" s="34">
+        <v>2.06E-2</v>
+      </c>
+      <c r="H27" s="34">
+        <v>2.8199999999999999E-2</v>
+      </c>
+      <c r="I27" s="34">
+        <v>4.02E-2</v>
+      </c>
+      <c r="J27" s="34">
+        <v>0.63149999999999995</v>
+      </c>
+      <c r="K27" s="34">
+        <v>2.7900000000000001E-2</v>
+      </c>
+      <c r="L27" s="34">
+        <v>2.81E-2</v>
+      </c>
+      <c r="M27" s="34">
+        <v>3.15E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="16">
+      <c r="A28" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="36">
+        <v>0.75439999999999996</v>
+      </c>
+      <c r="C28" s="36">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="D28" s="36">
+        <v>3.6600000000000001E-2</v>
+      </c>
+      <c r="E28" s="36">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="F28" s="36">
+        <v>0.75019999999999998</v>
+      </c>
+      <c r="G28" s="36">
+        <v>2.41E-2</v>
+      </c>
+      <c r="H28" s="36">
+        <v>3.6900000000000002E-2</v>
+      </c>
+      <c r="I28" s="36">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="J28" s="36">
+        <v>0.7258</v>
+      </c>
+      <c r="K28" s="36">
+        <v>4.1200000000000001E-2</v>
+      </c>
+      <c r="L28" s="36">
+        <v>6.0900000000000003E-2</v>
+      </c>
+      <c r="M28" s="36">
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="30"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="30"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="30"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="J17:M17"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D18" r:id="rId1" xr:uid="{704B4DC9-9EF2-FC44-822C-B9E2E35AD2FB}"/>
+    <hyperlink ref="H18" r:id="rId2" xr:uid="{41107FE4-BE69-7B41-A0CE-5CA481FFB681}"/>
+    <hyperlink ref="L18" r:id="rId3" xr:uid="{145F3887-2430-784A-B10C-C3522A2E54D4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/results.xlsx
+++ b/results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F30338E-A850-EA45-A236-EDE98318C1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6370F1C5-74B8-D94C-93E7-8978C47653B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="68">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -319,6 +319,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>MoGEAD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>MMoE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -371,10 +375,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>w/o Orth</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>w/o CE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -388,6 +388,94 @@
   </si>
   <si>
     <t>w/o IMNE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>w/o CSR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商业模拟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>recall</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>到的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>+β</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>价值</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>recall</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="SimSun"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>的审查成本为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>γ</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-0.01γ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ts=269</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ts=456</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ts=154</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>+R*β</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -583,7 +671,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -645,6 +733,13 @@
     <xf numFmtId="176" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -926,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:R52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -957,7 +1052,7 @@
       <c r="J1" s="24"/>
       <c r="K1" s="25"/>
       <c r="L1" s="26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M1" s="27"/>
       <c r="N1" s="27"/>
@@ -1809,7 +1904,7 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B25" s="3">
         <v>0.68120000000000003</v>
@@ -1848,7 +1943,7 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -1892,7 +1987,7 @@
         <v>6.5699999999999995E-2</v>
       </c>
       <c r="R26" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -1938,7 +2033,7 @@
     </row>
     <row r="28" spans="1:18">
       <c r="A28" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B28" s="6">
         <v>0.75439999999999996</v>
@@ -2201,7 +2296,7 @@
     </row>
     <row r="35" spans="1:18">
       <c r="A35" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B35" s="3">
         <v>0.74839999999999995</v>
@@ -2242,7 +2337,7 @@
     </row>
     <row r="36" spans="1:18">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B36" s="6">
         <v>0.75439999999999996</v>
@@ -2323,40 +2418,40 @@
       <c r="A39" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="3">
+      <c r="B39" s="37">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="37">
         <v>2.0500000000000001E-2</v>
       </c>
-      <c r="D39" s="3">
+      <c r="D39" s="37">
         <v>5.21E-2</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="37">
         <v>9.7699999999999995E-2</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="37">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="H39" s="4">
+      <c r="H39" s="37">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="I39" s="4">
+      <c r="I39" s="37">
         <v>4.7300000000000002E-2</v>
       </c>
-      <c r="J39" s="4">
+      <c r="J39" s="37">
         <v>9.8699999999999996E-2</v>
       </c>
-      <c r="L39" s="5">
+      <c r="L39" s="37">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="M39" s="5">
+      <c r="M39" s="37">
         <v>2.1100000000000001E-2</v>
       </c>
-      <c r="N39" s="5">
+      <c r="N39" s="37">
         <v>5.0900000000000001E-2</v>
       </c>
-      <c r="O39" s="12">
+      <c r="O39" s="38">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="R39" s="14" t="s">
@@ -2529,7 +2624,7 @@
     </row>
     <row r="44" spans="1:18">
       <c r="A44" s="10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B44" s="3">
         <v>3.6200000000000003E-2</v>
@@ -2572,82 +2667,117 @@
       <c r="A45" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3">
+      <c r="B45" s="37">
         <v>4.0399999999999998E-2</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="37">
         <v>9.7900000000000001E-2</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="37">
         <v>0.18540000000000001</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="37">
         <v>0.31440000000000001</v>
       </c>
-      <c r="G45" s="4">
+      <c r="G45" s="37">
         <v>3.6600000000000001E-2</v>
       </c>
-      <c r="H45" s="4">
+      <c r="H45" s="37">
         <v>8.43E-2</v>
       </c>
-      <c r="I45" s="4">
+      <c r="I45" s="37">
         <v>0.17530000000000001</v>
       </c>
-      <c r="J45" s="4">
+      <c r="J45" s="37">
         <v>0.30940000000000001</v>
       </c>
-      <c r="L45" s="5">
+      <c r="L45" s="37">
         <v>3.2599999999999997E-2</v>
       </c>
-      <c r="M45" s="5">
+      <c r="M45" s="37">
         <v>7.2099999999999997E-2</v>
       </c>
-      <c r="N45" s="5">
+      <c r="N45" s="37">
         <v>0.12570000000000001</v>
       </c>
-      <c r="O45" s="12">
+      <c r="O45" s="38">
         <v>0.2422</v>
       </c>
     </row>
     <row r="46" spans="1:18">
       <c r="A46" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="3">
+        <v>44</v>
+      </c>
+      <c r="B46" s="37">
         <v>5.0700000000000002E-2</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="39">
         <v>0.10920000000000001</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="37">
         <v>0.21540000000000001</v>
       </c>
-      <c r="E46" s="3">
+      <c r="E46" s="37">
         <v>0.34810000000000002</v>
       </c>
-      <c r="G46" s="4">
+      <c r="G46" s="37">
         <v>4.8099999999999997E-2</v>
       </c>
-      <c r="H46" s="7">
+      <c r="H46" s="39">
         <v>9.1600000000000001E-2</v>
       </c>
-      <c r="I46" s="4">
+      <c r="I46" s="37">
         <v>0.19420000000000001</v>
       </c>
-      <c r="J46" s="4">
+      <c r="J46" s="37">
         <v>0.33169999999999999</v>
       </c>
-      <c r="L46" s="5">
+      <c r="L46" s="37">
         <v>3.8899999999999997E-2</v>
       </c>
-      <c r="M46" s="8">
+      <c r="M46" s="39">
         <v>7.2599999999999998E-2</v>
       </c>
-      <c r="N46" s="5">
+      <c r="N46" s="37">
         <v>0.14249999999999999</v>
       </c>
-      <c r="O46" s="12">
+      <c r="O46" s="38">
         <v>0.26860000000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="G49" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="L49" s="43" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="40" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="41" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52" s="41" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2658,6 +2788,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -2677,12 +2808,12 @@
         <v>14</v>
       </c>
       <c r="D1" s="29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" s="29">
         <v>287195</v>
@@ -2696,7 +2827,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="29">
         <v>408239</v>
@@ -2710,7 +2841,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="29" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="29">
         <v>405543</v>
@@ -2724,7 +2855,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="29">
         <v>2696</v>
@@ -2767,7 +2898,7 @@
       <c r="H17" s="33"/>
       <c r="I17" s="33"/>
       <c r="J17" s="33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K17" s="33"/>
       <c r="L17" s="33"/>
@@ -2775,40 +2906,40 @@
     </row>
     <row r="18" spans="1:13" ht="16">
       <c r="A18" s="32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" s="34" t="s">
         <v>5</v>
       </c>
       <c r="D18" s="35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" s="34" t="s">
         <v>7</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" s="34" t="s">
         <v>5</v>
       </c>
       <c r="H18" s="35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I18" s="34" t="s">
         <v>7</v>
       </c>
       <c r="J18" s="34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K18" s="34" t="s">
         <v>5</v>
       </c>
       <c r="L18" s="35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M18" s="34" t="s">
         <v>7</v>
@@ -3062,7 +3193,7 @@
     </row>
     <row r="25" spans="1:13" ht="16">
       <c r="A25" s="31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="34">
         <v>0.68120000000000003</v>
@@ -3185,7 +3316,7 @@
     </row>
     <row r="28" spans="1:13" ht="16">
       <c r="A28" s="31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B28" s="36">
         <v>0.75439999999999996</v>

--- a/results.xlsx
+++ b/results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tinky2026/Documents/code/GeoGNNGraphDetect/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6370F1C5-74B8-D94C-93E7-8978C47653B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F88A5D-93DD-724B-8178-22247C188732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="63">
   <si>
     <t>metric</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -395,87 +395,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>商业模拟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>recall</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="SimSun"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>到的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>+β</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="SimSun"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>价值</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>recall</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="SimSun"/>
-        <family val="1"/>
-        <charset val="134"/>
-      </rPr>
-      <t>的审查成本为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>γ</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-0.01γ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ts=269</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ts=456</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ts=154</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>+R*β</t>
+    <t>Full</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mask10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mask20%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -671,7 +599,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -692,6 +620,23 @@
     <xf numFmtId="176" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="5" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -716,30 +661,12 @@
     <xf numFmtId="176" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1021,7 +948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R52"/>
+  <dimension ref="A1:R66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" style="1" customWidth="1"/>
@@ -1037,27 +964,27 @@
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="23" t="s">
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="26" t="s">
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
       <c r="R1" s="2" t="s">
         <v>2</v>
       </c>
@@ -2418,40 +2345,40 @@
       <c r="A39" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B39" s="37">
+      <c r="B39" s="28">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="C39" s="37">
+      <c r="C39" s="28">
         <v>2.0500000000000001E-2</v>
       </c>
-      <c r="D39" s="37">
+      <c r="D39" s="28">
         <v>5.21E-2</v>
       </c>
-      <c r="E39" s="37">
+      <c r="E39" s="28">
         <v>9.7699999999999995E-2</v>
       </c>
-      <c r="G39" s="37">
+      <c r="G39" s="28">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="H39" s="37">
+      <c r="H39" s="28">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="I39" s="37">
+      <c r="I39" s="28">
         <v>4.7300000000000002E-2</v>
       </c>
-      <c r="J39" s="37">
+      <c r="J39" s="28">
         <v>9.8699999999999996E-2</v>
       </c>
-      <c r="L39" s="37">
+      <c r="L39" s="28">
         <v>9.2999999999999992E-3</v>
       </c>
-      <c r="M39" s="37">
+      <c r="M39" s="28">
         <v>2.1100000000000001E-2</v>
       </c>
-      <c r="N39" s="37">
+      <c r="N39" s="28">
         <v>5.0900000000000001E-2</v>
       </c>
-      <c r="O39" s="38">
+      <c r="O39" s="29">
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="R39" s="14" t="s">
@@ -2667,40 +2594,40 @@
       <c r="A45" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="37">
+      <c r="B45" s="28">
         <v>4.0399999999999998E-2</v>
       </c>
-      <c r="C45" s="37">
+      <c r="C45" s="28">
         <v>9.7900000000000001E-2</v>
       </c>
-      <c r="D45" s="37">
+      <c r="D45" s="28">
         <v>0.18540000000000001</v>
       </c>
-      <c r="E45" s="37">
+      <c r="E45" s="28">
         <v>0.31440000000000001</v>
       </c>
-      <c r="G45" s="37">
+      <c r="G45" s="28">
         <v>3.6600000000000001E-2</v>
       </c>
-      <c r="H45" s="37">
+      <c r="H45" s="28">
         <v>8.43E-2</v>
       </c>
-      <c r="I45" s="37">
+      <c r="I45" s="28">
         <v>0.17530000000000001</v>
       </c>
-      <c r="J45" s="37">
+      <c r="J45" s="28">
         <v>0.30940000000000001</v>
       </c>
-      <c r="L45" s="37">
+      <c r="L45" s="28">
         <v>3.2599999999999997E-2</v>
       </c>
-      <c r="M45" s="37">
+      <c r="M45" s="28">
         <v>7.2099999999999997E-2</v>
       </c>
-      <c r="N45" s="37">
+      <c r="N45" s="28">
         <v>0.12570000000000001</v>
       </c>
-      <c r="O45" s="38">
+      <c r="O45" s="29">
         <v>0.2422</v>
       </c>
     </row>
@@ -2708,77 +2635,503 @@
       <c r="A46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="37">
+      <c r="B46" s="28">
         <v>5.0700000000000002E-2</v>
       </c>
-      <c r="C46" s="39">
+      <c r="C46" s="30">
         <v>0.10920000000000001</v>
       </c>
-      <c r="D46" s="37">
+      <c r="D46" s="28">
         <v>0.21540000000000001</v>
       </c>
-      <c r="E46" s="37">
+      <c r="E46" s="28">
         <v>0.34810000000000002</v>
       </c>
-      <c r="G46" s="37">
+      <c r="G46" s="28">
         <v>4.8099999999999997E-2</v>
       </c>
-      <c r="H46" s="39">
+      <c r="H46" s="30">
         <v>9.1600000000000001E-2</v>
       </c>
-      <c r="I46" s="37">
+      <c r="I46" s="28">
         <v>0.19420000000000001</v>
       </c>
-      <c r="J46" s="37">
+      <c r="J46" s="28">
         <v>0.33169999999999999</v>
       </c>
-      <c r="L46" s="37">
+      <c r="L46" s="28">
         <v>3.8899999999999997E-2</v>
       </c>
-      <c r="M46" s="39">
+      <c r="M46" s="30">
         <v>7.2599999999999998E-2</v>
       </c>
-      <c r="N46" s="37">
+      <c r="N46" s="28">
         <v>0.14249999999999999</v>
       </c>
-      <c r="O46" s="38">
+      <c r="O46" s="29">
         <v>0.26860000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
-      <c r="A49" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B49" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G49" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="L49" s="43" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12">
-      <c r="A50" s="40" t="s">
+    <row r="48" spans="1:18" s="23" customFormat="1">
+      <c r="A48" s="40"/>
+      <c r="B48" s="40"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="40"/>
+      <c r="H48" s="40"/>
+      <c r="I48" s="40"/>
+      <c r="J48" s="40"/>
+      <c r="K48" s="40"/>
+      <c r="L48" s="40"/>
+      <c r="M48" s="40"/>
+      <c r="N48" s="40"/>
+      <c r="O48" s="40"/>
+      <c r="P48" s="40"/>
+    </row>
+    <row r="49" spans="1:16" s="23" customFormat="1">
+      <c r="A49" s="40"/>
+      <c r="B49" s="40"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="40"/>
+      <c r="I49" s="40"/>
+      <c r="J49" s="40"/>
+      <c r="K49" s="40"/>
+      <c r="L49" s="40"/>
+      <c r="M49" s="40"/>
+      <c r="N49" s="40"/>
+      <c r="O49" s="40"/>
+      <c r="P49" s="40"/>
+    </row>
+    <row r="50" spans="1:16" s="23" customFormat="1">
+      <c r="A50" s="40"/>
+      <c r="B50" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="40"/>
+      <c r="J50" s="40"/>
+      <c r="K50" s="40"/>
+      <c r="L50" s="40"/>
+      <c r="M50" s="40"/>
+      <c r="N50" s="40"/>
+      <c r="O50" s="40"/>
+      <c r="P50" s="40"/>
+    </row>
+    <row r="51" spans="1:16" s="23" customFormat="1">
+      <c r="A51" s="40"/>
+      <c r="B51" s="23" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="1" t="s">
+      <c r="C51" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="B51" s="41" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" s="1" t="s">
+      <c r="D51" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="B52" s="41" t="s">
-        <v>63</v>
-      </c>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="H51" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="I51" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="J51" s="40"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="M51" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="N51" s="40" t="s">
+        <v>62</v>
+      </c>
+      <c r="O51" s="40"/>
+      <c r="P51" s="40"/>
+    </row>
+    <row r="52" spans="1:16" s="23" customFormat="1">
+      <c r="A52" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" s="40">
+        <v>5.2200000000000003E-2</v>
+      </c>
+      <c r="C52" s="40">
+        <v>4.4299999999999999E-2</v>
+      </c>
+      <c r="D52" s="40">
+        <v>3.78E-2</v>
+      </c>
+      <c r="E52" s="40"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="40">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="H52" s="40">
+        <v>4.3299999999999998E-2</v>
+      </c>
+      <c r="I52" s="40">
+        <v>3.5900000000000001E-2</v>
+      </c>
+      <c r="J52" s="40"/>
+      <c r="K52" s="40"/>
+      <c r="L52" s="40">
+        <v>6.3299999999999995E-2</v>
+      </c>
+      <c r="M52" s="40">
+        <v>5.3900000000000003E-2</v>
+      </c>
+      <c r="N52" s="40">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="O52" s="40"/>
+      <c r="P52" s="40"/>
+    </row>
+    <row r="53" spans="1:16" s="23" customFormat="1">
+      <c r="A53" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="B53" s="40">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="C53" s="40">
+        <v>4.2200000000000001E-2</v>
+      </c>
+      <c r="D53" s="40">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="40">
+        <v>5.1200000000000002E-2</v>
+      </c>
+      <c r="H53" s="40">
+        <v>4.3700000000000003E-2</v>
+      </c>
+      <c r="I53" s="40">
+        <v>3.78E-2</v>
+      </c>
+      <c r="J53" s="40"/>
+      <c r="K53" s="40"/>
+      <c r="L53" s="40">
+        <v>6.1899999999999997E-2</v>
+      </c>
+      <c r="M53" s="40">
+        <v>5.3600000000000002E-2</v>
+      </c>
+      <c r="N53" s="40">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="O53" s="40"/>
+      <c r="P53" s="40"/>
+    </row>
+    <row r="54" spans="1:16" s="23" customFormat="1">
+      <c r="A54" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54" s="40">
+        <v>4.7800000000000002E-2</v>
+      </c>
+      <c r="C54" s="40">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="D54" s="40">
+        <v>4.3099999999999999E-2</v>
+      </c>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40">
+        <v>4.7899999999999998E-2</v>
+      </c>
+      <c r="H54" s="40">
+        <v>4.58E-2</v>
+      </c>
+      <c r="I54" s="40">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="J54" s="40"/>
+      <c r="K54" s="40"/>
+      <c r="L54" s="40">
+        <v>5.3499999999999999E-2</v>
+      </c>
+      <c r="M54" s="40">
+        <v>5.21E-2</v>
+      </c>
+      <c r="N54" s="40">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="O54" s="40"/>
+      <c r="P54" s="40"/>
+    </row>
+    <row r="55" spans="1:16" s="23" customFormat="1">
+      <c r="A55" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B55" s="40">
+        <v>4.6600000000000003E-2</v>
+      </c>
+      <c r="C55" s="40">
+        <v>4.2500000000000003E-2</v>
+      </c>
+      <c r="D55" s="40">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40">
+        <v>4.48E-2</v>
+      </c>
+      <c r="H55" s="40">
+        <v>4.2200000000000001E-2</v>
+      </c>
+      <c r="I55" s="40">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="J55" s="40"/>
+      <c r="K55" s="40"/>
+      <c r="L55" s="40">
+        <v>6.2700000000000006E-2</v>
+      </c>
+      <c r="M55" s="40">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="N55" s="40">
+        <v>5.2900000000000003E-2</v>
+      </c>
+      <c r="O55" s="40"/>
+      <c r="P55" s="40"/>
+    </row>
+    <row r="56" spans="1:16" s="23" customFormat="1">
+      <c r="A56" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" s="42">
+        <v>5.4899999999999997E-2</v>
+      </c>
+      <c r="C56" s="42">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="D56" s="42">
+        <v>4.5499999999999999E-2</v>
+      </c>
+      <c r="E56" s="40"/>
+      <c r="F56" s="40"/>
+      <c r="G56" s="42">
+        <v>5.2600000000000001E-2</v>
+      </c>
+      <c r="H56" s="42">
+        <v>0.05</v>
+      </c>
+      <c r="I56" s="42">
+        <v>4.3400000000000001E-2</v>
+      </c>
+      <c r="J56" s="40"/>
+      <c r="K56" s="40"/>
+      <c r="L56" s="42">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="M56" s="42">
+        <v>6.1199999999999997E-2</v>
+      </c>
+      <c r="N56" s="42">
+        <v>5.5399999999999998E-2</v>
+      </c>
+      <c r="O56" s="40"/>
+      <c r="P56" s="40"/>
+    </row>
+    <row r="57" spans="1:16" s="23" customFormat="1">
+      <c r="A57" s="40"/>
+      <c r="B57" s="40"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="40"/>
+      <c r="I57" s="40"/>
+      <c r="J57" s="40"/>
+      <c r="K57" s="40"/>
+      <c r="L57" s="40"/>
+      <c r="M57" s="40"/>
+      <c r="N57" s="40"/>
+      <c r="O57" s="40"/>
+      <c r="P57" s="40"/>
+    </row>
+    <row r="58" spans="1:16" s="23" customFormat="1">
+      <c r="A58" s="40"/>
+      <c r="B58" s="40"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="40"/>
+      <c r="F58" s="40"/>
+      <c r="G58" s="40"/>
+      <c r="H58" s="40"/>
+      <c r="I58" s="40"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="40"/>
+      <c r="L58" s="40"/>
+      <c r="M58" s="40"/>
+      <c r="N58" s="40"/>
+      <c r="O58" s="40"/>
+      <c r="P58" s="40"/>
+    </row>
+    <row r="59" spans="1:16" s="23" customFormat="1">
+      <c r="A59" s="40"/>
+      <c r="B59" s="40"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
+      <c r="E59" s="40"/>
+      <c r="F59" s="40"/>
+      <c r="G59" s="40"/>
+      <c r="H59" s="40"/>
+      <c r="I59" s="40"/>
+      <c r="J59" s="40"/>
+      <c r="K59" s="40"/>
+      <c r="L59" s="40"/>
+      <c r="M59" s="40"/>
+      <c r="N59" s="40"/>
+      <c r="O59" s="41"/>
+      <c r="P59" s="40"/>
+    </row>
+    <row r="60" spans="1:16" s="23" customFormat="1">
+      <c r="A60" s="40"/>
+      <c r="B60" s="40"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="40"/>
+      <c r="I60" s="40"/>
+      <c r="J60" s="40"/>
+      <c r="K60" s="40"/>
+      <c r="L60" s="40"/>
+      <c r="M60" s="40"/>
+      <c r="N60" s="40"/>
+      <c r="O60" s="41"/>
+      <c r="P60" s="40"/>
+    </row>
+    <row r="61" spans="1:16" s="23" customFormat="1">
+      <c r="A61" s="40"/>
+      <c r="B61" s="40"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="40"/>
+      <c r="E61" s="40"/>
+      <c r="F61" s="40"/>
+      <c r="G61" s="40"/>
+      <c r="H61" s="40"/>
+      <c r="I61" s="40"/>
+      <c r="J61" s="40"/>
+      <c r="K61" s="40"/>
+      <c r="L61" s="40"/>
+      <c r="M61" s="40"/>
+      <c r="N61" s="40"/>
+      <c r="O61" s="41"/>
+      <c r="P61" s="40"/>
+    </row>
+    <row r="62" spans="1:16" s="23" customFormat="1">
+      <c r="A62" s="40"/>
+      <c r="B62" s="40"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="40"/>
+      <c r="E62" s="40"/>
+      <c r="F62" s="40"/>
+      <c r="G62" s="40"/>
+      <c r="H62" s="40"/>
+      <c r="I62" s="40"/>
+      <c r="J62" s="40"/>
+      <c r="K62" s="40"/>
+      <c r="L62" s="40"/>
+      <c r="M62" s="40"/>
+      <c r="N62" s="40"/>
+      <c r="O62" s="41"/>
+      <c r="P62" s="40"/>
+    </row>
+    <row r="63" spans="1:16" s="23" customFormat="1">
+      <c r="A63" s="40"/>
+      <c r="B63" s="40"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="40"/>
+      <c r="E63" s="40"/>
+      <c r="F63" s="40"/>
+      <c r="G63" s="40"/>
+      <c r="H63" s="40"/>
+      <c r="I63" s="40"/>
+      <c r="J63" s="40"/>
+      <c r="K63" s="40"/>
+      <c r="L63" s="40"/>
+      <c r="M63" s="40"/>
+      <c r="N63" s="40"/>
+      <c r="O63" s="41"/>
+      <c r="P63" s="40"/>
+    </row>
+    <row r="64" spans="1:16" s="23" customFormat="1">
+      <c r="A64" s="40"/>
+      <c r="B64" s="40"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="40"/>
+      <c r="E64" s="40"/>
+      <c r="F64" s="40"/>
+      <c r="G64" s="40"/>
+      <c r="H64" s="40"/>
+      <c r="I64" s="40"/>
+      <c r="J64" s="40"/>
+      <c r="K64" s="40"/>
+      <c r="L64" s="40"/>
+      <c r="M64" s="40"/>
+      <c r="N64" s="40"/>
+      <c r="O64" s="41"/>
+      <c r="P64" s="40"/>
+    </row>
+    <row r="65" spans="1:16" s="23" customFormat="1">
+      <c r="A65" s="40"/>
+      <c r="B65" s="40"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="40"/>
+      <c r="F65" s="40"/>
+      <c r="G65" s="40"/>
+      <c r="H65" s="40"/>
+      <c r="I65" s="40"/>
+      <c r="J65" s="40"/>
+      <c r="K65" s="40"/>
+      <c r="L65" s="40"/>
+      <c r="M65" s="40"/>
+      <c r="N65" s="40"/>
+      <c r="O65" s="41"/>
+      <c r="P65" s="40"/>
+    </row>
+    <row r="66" spans="1:16" s="23" customFormat="1">
+      <c r="A66" s="40"/>
+      <c r="B66" s="40"/>
+      <c r="C66" s="40"/>
+      <c r="D66" s="40"/>
+      <c r="E66" s="40"/>
+      <c r="F66" s="40"/>
+      <c r="G66" s="40"/>
+      <c r="H66" s="40"/>
+      <c r="I66" s="40"/>
+      <c r="J66" s="40"/>
+      <c r="K66" s="40"/>
+      <c r="L66" s="40"/>
+      <c r="M66" s="40"/>
+      <c r="N66" s="40"/>
+      <c r="O66" s="41"/>
+      <c r="P66" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2798,590 +3151,590 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="21" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="21">
         <v>287195</v>
       </c>
-      <c r="C2" s="29">
+      <c r="C2" s="21">
         <v>410223</v>
       </c>
-      <c r="D2" s="29">
+      <c r="D2" s="21">
         <v>48843</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="29">
+      <c r="B3" s="21">
         <v>408239</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="21">
         <v>568694</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="21">
         <v>85590</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="29">
+      <c r="B4" s="21">
         <v>405543</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="21">
         <v>564129</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="21">
         <v>84136</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="29">
+      <c r="B5" s="21">
         <v>2696</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="21">
         <v>4565</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="21">
         <v>1454</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-    </row>
-    <row r="17" spans="1:13" s="28" customFormat="1" ht="14">
-      <c r="A17" s="32" t="s">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+    </row>
+    <row r="17" spans="1:13" s="20" customFormat="1" ht="14">
+      <c r="A17" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33" t="s">
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33" t="s">
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
     </row>
     <row r="18" spans="1:13" ht="16">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="34" t="s">
+      <c r="C18" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="35" t="s">
+      <c r="D18" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="34" t="s">
+      <c r="F18" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="34" t="s">
+      <c r="G18" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="35" t="s">
+      <c r="H18" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="I18" s="34" t="s">
+      <c r="I18" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="J18" s="34" t="s">
+      <c r="J18" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="K18" s="34" t="s">
+      <c r="K18" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="L18" s="35" t="s">
+      <c r="L18" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="M18" s="34" t="s">
+      <c r="M18" s="25" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="16">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="25">
         <v>0.50019999999999998</v>
       </c>
-      <c r="C19" s="34">
+      <c r="C19" s="25">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="D19" s="34">
+      <c r="D19" s="25">
         <v>6.7000000000000002E-3</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="25">
         <v>1.01E-2</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="25">
         <v>0.5</v>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="25">
         <v>8.0999999999999996E-3</v>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="25">
         <v>6.6E-3</v>
       </c>
-      <c r="I19" s="34">
+      <c r="I19" s="25">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="J19" s="34">
+      <c r="J19" s="25">
         <v>0.504</v>
       </c>
-      <c r="K19" s="34">
+      <c r="K19" s="25">
         <v>1.84E-2</v>
       </c>
-      <c r="L19" s="34">
+      <c r="L19" s="25">
         <v>1.7399999999999999E-2</v>
       </c>
-      <c r="M19" s="34">
+      <c r="M19" s="25">
         <v>1.9099999999999999E-2</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="16">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="34">
+      <c r="B20" s="25">
         <v>0.61499999999999999</v>
       </c>
-      <c r="C20" s="34">
+      <c r="C20" s="25">
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="D20" s="34">
+      <c r="D20" s="25">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="E20" s="34">
+      <c r="E20" s="25">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="25">
         <v>0.60599999999999998</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="25">
         <v>1.09E-2</v>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="25">
         <v>1.11E-2</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="25">
         <v>1.61E-2</v>
       </c>
-      <c r="J20" s="34">
+      <c r="J20" s="25">
         <v>0.62150000000000005</v>
       </c>
-      <c r="K20" s="34">
+      <c r="K20" s="25">
         <v>2.5700000000000001E-2</v>
       </c>
-      <c r="L20" s="34">
+      <c r="L20" s="25">
         <v>2.8500000000000001E-2</v>
       </c>
-      <c r="M20" s="34">
+      <c r="M20" s="25">
         <v>3.2800000000000003E-2</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="16">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="34">
+      <c r="B21" s="25">
         <v>0.67200000000000004</v>
       </c>
-      <c r="C21" s="34">
+      <c r="C21" s="25">
         <v>1.3599999999999999E-2</v>
       </c>
-      <c r="D21" s="34">
+      <c r="D21" s="25">
         <v>1.77E-2</v>
       </c>
-      <c r="E21" s="34">
+      <c r="E21" s="25">
         <v>2.6599999999999999E-2</v>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="25">
         <v>0.64049999999999996</v>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="25">
         <v>1.35E-2</v>
       </c>
-      <c r="H21" s="34">
+      <c r="H21" s="25">
         <v>1.44E-2</v>
       </c>
-      <c r="I21" s="34">
+      <c r="I21" s="25">
         <v>2.06E-2</v>
       </c>
-      <c r="J21" s="34">
+      <c r="J21" s="25">
         <v>0.63139999999999996</v>
       </c>
-      <c r="K21" s="34">
+      <c r="K21" s="25">
         <v>3.1199999999999999E-2</v>
       </c>
-      <c r="L21" s="34">
+      <c r="L21" s="25">
         <v>4.1799999999999997E-2</v>
       </c>
-      <c r="M21" s="34">
+      <c r="M21" s="25">
         <v>4.53E-2</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="16">
-      <c r="A22" s="31" t="s">
+      <c r="A22" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="34">
+      <c r="B22" s="25">
         <v>0.67730000000000001</v>
       </c>
-      <c r="C22" s="34">
+      <c r="C22" s="25">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="D22" s="34">
+      <c r="D22" s="25">
         <v>1.6899999999999998E-2</v>
       </c>
-      <c r="E22" s="34">
+      <c r="E22" s="25">
         <v>2.5600000000000001E-2</v>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="25">
         <v>0.67310000000000003</v>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="25">
         <v>1.4800000000000001E-2</v>
       </c>
-      <c r="H22" s="34">
+      <c r="H22" s="25">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="I22" s="34">
+      <c r="I22" s="25">
         <v>2.8199999999999999E-2</v>
       </c>
-      <c r="J22" s="34">
+      <c r="J22" s="25">
         <v>0.68069999999999997</v>
       </c>
-      <c r="K22" s="34">
+      <c r="K22" s="25">
         <v>3.2500000000000001E-2</v>
       </c>
-      <c r="L22" s="34">
+      <c r="L22" s="25">
         <v>4.58E-2</v>
       </c>
-      <c r="M22" s="34">
+      <c r="M22" s="25">
         <v>5.0799999999999998E-2</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="16">
-      <c r="A23" s="31" t="s">
+      <c r="A23" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="34">
+      <c r="B23" s="25">
         <v>0.67020000000000002</v>
       </c>
-      <c r="C23" s="34">
+      <c r="C23" s="25">
         <v>1.1900000000000001E-2</v>
       </c>
-      <c r="D23" s="34">
+      <c r="D23" s="25">
         <v>1.4200000000000001E-2</v>
       </c>
-      <c r="E23" s="34">
+      <c r="E23" s="25">
         <v>2.1499999999999998E-2</v>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="25">
         <v>0.67569999999999997</v>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="25">
         <v>1.5299999999999999E-2</v>
       </c>
-      <c r="H23" s="34">
+      <c r="H23" s="25">
         <v>2.0500000000000001E-2</v>
       </c>
-      <c r="I23" s="34">
+      <c r="I23" s="25">
         <v>2.92E-2</v>
       </c>
-      <c r="J23" s="34">
+      <c r="J23" s="25">
         <v>0.67300000000000004</v>
       </c>
-      <c r="K23" s="34">
+      <c r="K23" s="25">
         <v>3.4200000000000001E-2</v>
       </c>
-      <c r="L23" s="34">
+      <c r="L23" s="25">
         <v>4.6899999999999997E-2</v>
       </c>
-      <c r="M23" s="34">
+      <c r="M23" s="25">
         <v>5.2400000000000002E-2</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="16">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="34">
+      <c r="B24" s="25">
         <v>0.66910000000000003</v>
       </c>
-      <c r="C24" s="34">
+      <c r="C24" s="25">
         <v>1.4E-2</v>
       </c>
-      <c r="D24" s="34">
+      <c r="D24" s="25">
         <v>1.84E-2</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="25">
         <v>2.6700000000000002E-2</v>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="25">
         <v>0.66759999999999997</v>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="25">
         <v>1.55E-2</v>
       </c>
-      <c r="H24" s="34">
+      <c r="H24" s="25">
         <v>2.12E-2</v>
       </c>
-      <c r="I24" s="34">
+      <c r="I24" s="25">
         <v>3.44E-2</v>
       </c>
-      <c r="J24" s="34">
+      <c r="J24" s="25">
         <v>0.67400000000000004</v>
       </c>
-      <c r="K24" s="34">
+      <c r="K24" s="25">
         <v>3.0599999999999999E-2</v>
       </c>
-      <c r="L24" s="34">
+      <c r="L24" s="25">
         <v>4.9099999999999998E-2</v>
       </c>
-      <c r="M24" s="34">
+      <c r="M24" s="25">
         <v>5.4899999999999997E-2</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="16">
-      <c r="A25" s="31" t="s">
+      <c r="A25" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="34">
+      <c r="B25" s="25">
         <v>0.68120000000000003</v>
       </c>
-      <c r="C25" s="34">
+      <c r="C25" s="25">
         <v>1.6E-2</v>
       </c>
-      <c r="D25" s="34">
+      <c r="D25" s="25">
         <v>2.47E-2</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="25">
         <v>3.7100000000000001E-2</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="25">
         <v>0.69889999999999997</v>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="25">
         <v>1.9800000000000002E-2</v>
       </c>
-      <c r="H25" s="34">
+      <c r="H25" s="25">
         <v>2.86E-2</v>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="25">
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="J25" s="34">
+      <c r="J25" s="25">
         <v>0.62560000000000004</v>
       </c>
-      <c r="K25" s="34">
+      <c r="K25" s="25">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="L25" s="34">
+      <c r="L25" s="25">
         <v>3.3099999999999997E-2</v>
       </c>
-      <c r="M25" s="34">
+      <c r="M25" s="25">
         <v>3.5900000000000001E-2</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="16">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="34">
+      <c r="B26" s="25">
         <v>0.74639999999999995</v>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="25">
         <v>1.9599999999999999E-2</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="25">
         <v>3.2300000000000002E-2</v>
       </c>
-      <c r="E26" s="34">
+      <c r="E26" s="25">
         <v>4.8500000000000001E-2</v>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="25">
         <v>0.73980000000000001</v>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="25">
         <v>2.23E-2</v>
       </c>
-      <c r="H26" s="34">
+      <c r="H26" s="25">
         <v>3.3799999999999997E-2</v>
       </c>
-      <c r="I26" s="34">
+      <c r="I26" s="25">
         <v>4.8300000000000003E-2</v>
       </c>
-      <c r="J26" s="34">
+      <c r="J26" s="25">
         <v>0.71360000000000001</v>
       </c>
-      <c r="K26" s="34">
+      <c r="K26" s="25">
         <v>3.9699999999999999E-2</v>
       </c>
-      <c r="L26" s="34">
+      <c r="L26" s="25">
         <v>6.0400000000000002E-2</v>
       </c>
-      <c r="M26" s="34">
+      <c r="M26" s="25">
         <v>6.5699999999999995E-2</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="16">
-      <c r="A27" s="31" t="s">
+      <c r="A27" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="34">
+      <c r="B27" s="25">
         <v>0.68169999999999997</v>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="25">
         <v>1.5599999999999999E-2</v>
       </c>
-      <c r="D27" s="34">
+      <c r="D27" s="25">
         <v>2.01E-2</v>
       </c>
-      <c r="E27" s="34">
+      <c r="E27" s="25">
         <v>3.0200000000000001E-2</v>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="25">
         <v>0.72240000000000004</v>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="25">
         <v>2.06E-2</v>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="25">
         <v>2.8199999999999999E-2</v>
       </c>
-      <c r="I27" s="34">
+      <c r="I27" s="25">
         <v>4.02E-2</v>
       </c>
-      <c r="J27" s="34">
+      <c r="J27" s="25">
         <v>0.63149999999999995</v>
       </c>
-      <c r="K27" s="34">
+      <c r="K27" s="25">
         <v>2.7900000000000001E-2</v>
       </c>
-      <c r="L27" s="34">
+      <c r="L27" s="25">
         <v>2.81E-2</v>
       </c>
-      <c r="M27" s="34">
+      <c r="M27" s="25">
         <v>3.15E-2</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="16">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="36">
+      <c r="B28" s="27">
         <v>0.75439999999999996</v>
       </c>
-      <c r="C28" s="36">
+      <c r="C28" s="27">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="D28" s="36">
+      <c r="D28" s="27">
         <v>3.6600000000000001E-2</v>
       </c>
-      <c r="E28" s="36">
+      <c r="E28" s="27">
         <v>5.4899999999999997E-2</v>
       </c>
-      <c r="F28" s="36">
+      <c r="F28" s="27">
         <v>0.75019999999999998</v>
       </c>
-      <c r="G28" s="36">
+      <c r="G28" s="27">
         <v>2.41E-2</v>
       </c>
-      <c r="H28" s="36">
+      <c r="H28" s="27">
         <v>3.6900000000000002E-2</v>
       </c>
-      <c r="I28" s="36">
+      <c r="I28" s="27">
         <v>5.2600000000000001E-2</v>
       </c>
-      <c r="J28" s="36">
+      <c r="J28" s="27">
         <v>0.7258</v>
       </c>
-      <c r="K28" s="36">
+      <c r="K28" s="27">
         <v>4.1200000000000001E-2</v>
       </c>
-      <c r="L28" s="36">
+      <c r="L28" s="27">
         <v>6.0900000000000003E-2</v>
       </c>
-      <c r="M28" s="36">
+      <c r="M28" s="27">
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
     <row r="29" spans="1:13">
-      <c r="A29" s="30"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
     </row>
     <row r="30" spans="1:13">
-      <c r="A30" s="30"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
     </row>
     <row r="31" spans="1:13">
-      <c r="A31" s="30"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
     </row>
     <row r="32" spans="1:13">
-      <c r="A32" s="30"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="3">
